--- a/Prototypes/KiwiFruit/HC_Observations.xlsx
+++ b/Prototypes/KiwiFruit/HC_Observations.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitHub repos\APSIMX\Prototypes\KiwiFruit\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7F8000EE-2504-416C-A6B5-04130D59F2D3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7DCE3579-6E57-4FA2-B5BD-9AB138B15A22}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -131,43 +131,13 @@
     <t>TPHaywardBB20186%HC+0.2%DS231</t>
   </si>
   <si>
-    <t>KKHaywardBB2018HiCane6%+0.2%Driftstop239</t>
-  </si>
-  <si>
     <t>HiCane 6% + 0.2% Driftstop</t>
-  </si>
-  <si>
-    <t>KKHaywardBB2018HiCane6%+0.2%Driftstop248</t>
-  </si>
-  <si>
-    <t>HaywardBB2019HC6%+0.2%DS236</t>
   </si>
   <si>
     <t>HC 6% + 0.2%DS</t>
   </si>
   <si>
-    <t>HaywardBB2019HC6%+0.2%DS243</t>
-  </si>
-  <si>
-    <t>HWBBRaw2020HiCane+Driftstop240</t>
-  </si>
-  <si>
     <t>HiCane+Driftstop</t>
-  </si>
-  <si>
-    <t>HWBBRaw2020HiCane+Driftstop235</t>
-  </si>
-  <si>
-    <t>HWBBRaw2020HiCane+Driftstop247</t>
-  </si>
-  <si>
-    <t>HWBBSpray2020HiCane+Driftstop248</t>
-  </si>
-  <si>
-    <t>HWBBSpray2020HiCane+Driftstop232</t>
-  </si>
-  <si>
-    <t>HWBBSpray2020HiCane+Driftstop243</t>
   </si>
   <si>
     <t>HW-BudbreakTP2020HiCane231</t>
@@ -208,13 +178,43 @@
   <si>
     <t>KiwiFruit.Phenology.FloweringDOY</t>
   </si>
+  <si>
+    <t>KKHaywardBB2018HiCaneDriftstop239</t>
+  </si>
+  <si>
+    <t>KKHaywardBB2018HiCaneDriftstop248</t>
+  </si>
+  <si>
+    <t>HaywardBB2019HCDS236</t>
+  </si>
+  <si>
+    <t>HaywardBB2019HCDS243</t>
+  </si>
+  <si>
+    <t>HWBBRaw2020HiCaneDriftstop240</t>
+  </si>
+  <si>
+    <t>HWBBRaw2020HiCaneDriftstop235</t>
+  </si>
+  <si>
+    <t>HWBBRaw2020HiCaneDriftstop247</t>
+  </si>
+  <si>
+    <t>HWBBSpray2020HiCaneDriftstop248</t>
+  </si>
+  <si>
+    <t>HWBBSpray2020HiCaneDriftstop232</t>
+  </si>
+  <si>
+    <t>HWBBSpray2020HiCaneDriftstop243</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
-    <numFmt numFmtId="165" formatCode="yyyy\-mm\-dd\ hh:mm:ss"/>
+    <numFmt numFmtId="164" formatCode="yyyy\-mm\-dd\ hh:mm:ss"/>
   </numFmts>
   <fonts count="2" x14ac:knownFonts="1">
     <font>
@@ -270,7 +270,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -575,6 +575,9 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:K507"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="74.33203125" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
@@ -5744,7 +5747,7 @@
     </row>
     <row r="175" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A175" t="s">
-        <v>36</v>
+        <v>52</v>
       </c>
       <c r="B175" s="2">
         <v>43353</v>
@@ -5759,7 +5762,7 @@
         <v>25</v>
       </c>
       <c r="F175" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="G175">
         <v>0</v>
@@ -5773,7 +5776,7 @@
     </row>
     <row r="176" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A176" t="s">
-        <v>36</v>
+        <v>52</v>
       </c>
       <c r="B176" s="2">
         <v>43356</v>
@@ -5788,7 +5791,7 @@
         <v>25</v>
       </c>
       <c r="F176" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="G176">
         <v>0</v>
@@ -5802,7 +5805,7 @@
     </row>
     <row r="177" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A177" t="s">
-        <v>36</v>
+        <v>52</v>
       </c>
       <c r="B177" s="2">
         <v>43360</v>
@@ -5817,7 +5820,7 @@
         <v>25</v>
       </c>
       <c r="F177" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="G177">
         <v>0</v>
@@ -5831,7 +5834,7 @@
     </row>
     <row r="178" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A178" t="s">
-        <v>36</v>
+        <v>52</v>
       </c>
       <c r="B178" s="2">
         <v>43363</v>
@@ -5846,7 +5849,7 @@
         <v>25</v>
       </c>
       <c r="F178" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="G178">
         <v>0</v>
@@ -5860,7 +5863,7 @@
     </row>
     <row r="179" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A179" t="s">
-        <v>36</v>
+        <v>52</v>
       </c>
       <c r="B179" s="2">
         <v>43367</v>
@@ -5875,7 +5878,7 @@
         <v>25</v>
       </c>
       <c r="F179" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="G179">
         <v>0</v>
@@ -5889,7 +5892,7 @@
     </row>
     <row r="180" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A180" t="s">
-        <v>36</v>
+        <v>52</v>
       </c>
       <c r="B180" s="2">
         <v>43370</v>
@@ -5904,7 +5907,7 @@
         <v>25</v>
       </c>
       <c r="F180" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="G180">
         <v>0</v>
@@ -5918,7 +5921,7 @@
     </row>
     <row r="181" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A181" t="s">
-        <v>36</v>
+        <v>52</v>
       </c>
       <c r="B181" s="2">
         <v>43374</v>
@@ -5933,7 +5936,7 @@
         <v>25</v>
       </c>
       <c r="F181" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="G181">
         <v>2</v>
@@ -5947,7 +5950,7 @@
     </row>
     <row r="182" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A182" t="s">
-        <v>36</v>
+        <v>52</v>
       </c>
       <c r="B182" s="2">
         <v>43377</v>
@@ -5962,7 +5965,7 @@
         <v>25</v>
       </c>
       <c r="F182" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="G182">
         <v>4</v>
@@ -5976,7 +5979,7 @@
     </row>
     <row r="183" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A183" t="s">
-        <v>36</v>
+        <v>52</v>
       </c>
       <c r="B183" s="2">
         <v>43381</v>
@@ -5991,7 +5994,7 @@
         <v>25</v>
       </c>
       <c r="F183" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="G183">
         <v>6</v>
@@ -6005,7 +6008,7 @@
     </row>
     <row r="184" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A184" t="s">
-        <v>36</v>
+        <v>52</v>
       </c>
       <c r="B184" s="2">
         <v>43384</v>
@@ -6020,7 +6023,7 @@
         <v>25</v>
       </c>
       <c r="F184" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="G184">
         <v>6</v>
@@ -6034,7 +6037,7 @@
     </row>
     <row r="185" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A185" t="s">
-        <v>36</v>
+        <v>52</v>
       </c>
       <c r="B185" s="2">
         <v>43388</v>
@@ -6049,7 +6052,7 @@
         <v>25</v>
       </c>
       <c r="F185" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="G185">
         <v>7</v>
@@ -6063,7 +6066,7 @@
     </row>
     <row r="186" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A186" t="s">
-        <v>36</v>
+        <v>52</v>
       </c>
       <c r="B186" s="2">
         <v>43392</v>
@@ -6078,7 +6081,7 @@
         <v>25</v>
       </c>
       <c r="F186" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="G186">
         <v>7</v>
@@ -6092,7 +6095,7 @@
     </row>
     <row r="187" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A187" t="s">
-        <v>36</v>
+        <v>52</v>
       </c>
       <c r="B187" s="2">
         <v>43396</v>
@@ -6107,7 +6110,7 @@
         <v>25</v>
       </c>
       <c r="F187" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="G187">
         <v>7</v>
@@ -6121,7 +6124,7 @@
     </row>
     <row r="188" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A188" t="s">
-        <v>36</v>
+        <v>52</v>
       </c>
       <c r="B188" s="2">
         <v>43399</v>
@@ -6136,7 +6139,7 @@
         <v>25</v>
       </c>
       <c r="F188" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="G188">
         <v>7</v>
@@ -6150,7 +6153,7 @@
     </row>
     <row r="189" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A189" t="s">
-        <v>36</v>
+        <v>52</v>
       </c>
       <c r="B189" s="2">
         <v>43404</v>
@@ -6165,7 +6168,7 @@
         <v>25</v>
       </c>
       <c r="F189" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="G189">
         <v>7</v>
@@ -6179,7 +6182,7 @@
     </row>
     <row r="190" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A190" t="s">
-        <v>36</v>
+        <v>52</v>
       </c>
       <c r="B190" s="2">
         <v>43410</v>
@@ -6194,7 +6197,7 @@
         <v>25</v>
       </c>
       <c r="F190" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="G190">
         <v>7</v>
@@ -6214,7 +6217,7 @@
     </row>
     <row r="191" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A191" t="s">
-        <v>38</v>
+        <v>53</v>
       </c>
       <c r="B191" s="2">
         <v>43353</v>
@@ -6229,7 +6232,7 @@
         <v>25</v>
       </c>
       <c r="F191" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="G191">
         <v>0</v>
@@ -6243,7 +6246,7 @@
     </row>
     <row r="192" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A192" t="s">
-        <v>38</v>
+        <v>53</v>
       </c>
       <c r="B192" s="2">
         <v>43356</v>
@@ -6258,7 +6261,7 @@
         <v>25</v>
       </c>
       <c r="F192" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="G192">
         <v>0</v>
@@ -6272,7 +6275,7 @@
     </row>
     <row r="193" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A193" t="s">
-        <v>38</v>
+        <v>53</v>
       </c>
       <c r="B193" s="2">
         <v>43360</v>
@@ -6287,7 +6290,7 @@
         <v>25</v>
       </c>
       <c r="F193" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="G193">
         <v>0</v>
@@ -6301,7 +6304,7 @@
     </row>
     <row r="194" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A194" t="s">
-        <v>38</v>
+        <v>53</v>
       </c>
       <c r="B194" s="2">
         <v>43363</v>
@@ -6316,7 +6319,7 @@
         <v>25</v>
       </c>
       <c r="F194" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="G194">
         <v>0</v>
@@ -6330,7 +6333,7 @@
     </row>
     <row r="195" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A195" t="s">
-        <v>38</v>
+        <v>53</v>
       </c>
       <c r="B195" s="2">
         <v>43367</v>
@@ -6345,7 +6348,7 @@
         <v>25</v>
       </c>
       <c r="F195" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="G195">
         <v>0</v>
@@ -6359,7 +6362,7 @@
     </row>
     <row r="196" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A196" t="s">
-        <v>38</v>
+        <v>53</v>
       </c>
       <c r="B196" s="2">
         <v>43370</v>
@@ -6374,7 +6377,7 @@
         <v>25</v>
       </c>
       <c r="F196" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="G196">
         <v>0</v>
@@ -6388,7 +6391,7 @@
     </row>
     <row r="197" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A197" t="s">
-        <v>38</v>
+        <v>53</v>
       </c>
       <c r="B197" s="2">
         <v>43374</v>
@@ -6403,7 +6406,7 @@
         <v>25</v>
       </c>
       <c r="F197" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="G197">
         <v>0</v>
@@ -6417,7 +6420,7 @@
     </row>
     <row r="198" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A198" t="s">
-        <v>38</v>
+        <v>53</v>
       </c>
       <c r="B198" s="2">
         <v>43377</v>
@@ -6432,7 +6435,7 @@
         <v>25</v>
       </c>
       <c r="F198" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="G198">
         <v>1</v>
@@ -6446,7 +6449,7 @@
     </row>
     <row r="199" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A199" t="s">
-        <v>38</v>
+        <v>53</v>
       </c>
       <c r="B199" s="2">
         <v>43381</v>
@@ -6461,7 +6464,7 @@
         <v>25</v>
       </c>
       <c r="F199" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="G199">
         <v>3</v>
@@ -6475,7 +6478,7 @@
     </row>
     <row r="200" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A200" t="s">
-        <v>38</v>
+        <v>53</v>
       </c>
       <c r="B200" s="2">
         <v>43384</v>
@@ -6490,7 +6493,7 @@
         <v>25</v>
       </c>
       <c r="F200" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="G200">
         <v>4</v>
@@ -6504,7 +6507,7 @@
     </row>
     <row r="201" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A201" t="s">
-        <v>38</v>
+        <v>53</v>
       </c>
       <c r="B201" s="2">
         <v>43388</v>
@@ -6519,7 +6522,7 @@
         <v>25</v>
       </c>
       <c r="F201" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="G201">
         <v>5.5</v>
@@ -6533,7 +6536,7 @@
     </row>
     <row r="202" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A202" t="s">
-        <v>38</v>
+        <v>53</v>
       </c>
       <c r="B202" s="2">
         <v>43392</v>
@@ -6548,7 +6551,7 @@
         <v>25</v>
       </c>
       <c r="F202" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="G202">
         <v>6</v>
@@ -6562,7 +6565,7 @@
     </row>
     <row r="203" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A203" t="s">
-        <v>38</v>
+        <v>53</v>
       </c>
       <c r="B203" s="2">
         <v>43396</v>
@@ -6577,7 +6580,7 @@
         <v>25</v>
       </c>
       <c r="F203" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="G203">
         <v>6.5</v>
@@ -6591,7 +6594,7 @@
     </row>
     <row r="204" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A204" t="s">
-        <v>38</v>
+        <v>53</v>
       </c>
       <c r="B204" s="2">
         <v>43399</v>
@@ -6606,7 +6609,7 @@
         <v>25</v>
       </c>
       <c r="F204" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="G204">
         <v>6.5</v>
@@ -6620,7 +6623,7 @@
     </row>
     <row r="205" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A205" t="s">
-        <v>38</v>
+        <v>53</v>
       </c>
       <c r="B205" s="2">
         <v>43404</v>
@@ -6635,7 +6638,7 @@
         <v>25</v>
       </c>
       <c r="F205" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="G205">
         <v>6.5</v>
@@ -6649,7 +6652,7 @@
     </row>
     <row r="206" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A206" t="s">
-        <v>38</v>
+        <v>53</v>
       </c>
       <c r="B206" s="2">
         <v>43410</v>
@@ -6664,7 +6667,7 @@
         <v>25</v>
       </c>
       <c r="F206" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="G206">
         <v>7</v>
@@ -6684,7 +6687,7 @@
     </row>
     <row r="207" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A207" t="s">
-        <v>39</v>
+        <v>54</v>
       </c>
       <c r="B207" s="2">
         <v>43720</v>
@@ -6699,7 +6702,7 @@
         <v>25</v>
       </c>
       <c r="F207" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="G207">
         <v>0</v>
@@ -6713,7 +6716,7 @@
     </row>
     <row r="208" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A208" t="s">
-        <v>39</v>
+        <v>54</v>
       </c>
       <c r="B208" s="2">
         <v>43724</v>
@@ -6728,7 +6731,7 @@
         <v>25</v>
       </c>
       <c r="F208" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="G208">
         <v>0</v>
@@ -6742,7 +6745,7 @@
     </row>
     <row r="209" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A209" t="s">
-        <v>39</v>
+        <v>54</v>
       </c>
       <c r="B209" s="2">
         <v>43727</v>
@@ -6757,7 +6760,7 @@
         <v>25</v>
       </c>
       <c r="F209" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="G209">
         <v>0</v>
@@ -6771,7 +6774,7 @@
     </row>
     <row r="210" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A210" t="s">
-        <v>39</v>
+        <v>54</v>
       </c>
       <c r="B210" s="2">
         <v>43731</v>
@@ -6786,7 +6789,7 @@
         <v>25</v>
       </c>
       <c r="F210" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="G210">
         <v>0</v>
@@ -6800,7 +6803,7 @@
     </row>
     <row r="211" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A211" t="s">
-        <v>39</v>
+        <v>54</v>
       </c>
       <c r="B211" s="2">
         <v>43734</v>
@@ -6815,7 +6818,7 @@
         <v>25</v>
       </c>
       <c r="F211" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="G211">
         <v>2</v>
@@ -6829,7 +6832,7 @@
     </row>
     <row r="212" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A212" t="s">
-        <v>39</v>
+        <v>54</v>
       </c>
       <c r="B212" s="2">
         <v>43738</v>
@@ -6844,7 +6847,7 @@
         <v>25</v>
       </c>
       <c r="F212" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="G212">
         <v>6</v>
@@ -6858,7 +6861,7 @@
     </row>
     <row r="213" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A213" t="s">
-        <v>39</v>
+        <v>54</v>
       </c>
       <c r="B213" s="2">
         <v>43741</v>
@@ -6873,7 +6876,7 @@
         <v>25</v>
       </c>
       <c r="F213" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="G213">
         <v>7.5</v>
@@ -6887,7 +6890,7 @@
     </row>
     <row r="214" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A214" t="s">
-        <v>39</v>
+        <v>54</v>
       </c>
       <c r="B214" s="2">
         <v>43745</v>
@@ -6902,7 +6905,7 @@
         <v>25</v>
       </c>
       <c r="F214" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="G214">
         <v>8</v>
@@ -6916,7 +6919,7 @@
     </row>
     <row r="215" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A215" t="s">
-        <v>39</v>
+        <v>54</v>
       </c>
       <c r="B215" s="2">
         <v>43748</v>
@@ -6931,7 +6934,7 @@
         <v>25</v>
       </c>
       <c r="F215" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="G215">
         <v>8.5</v>
@@ -6945,7 +6948,7 @@
     </row>
     <row r="216" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A216" t="s">
-        <v>39</v>
+        <v>54</v>
       </c>
       <c r="B216" s="2">
         <v>43752</v>
@@ -6960,7 +6963,7 @@
         <v>25</v>
       </c>
       <c r="F216" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="G216">
         <v>8.5</v>
@@ -6974,7 +6977,7 @@
     </row>
     <row r="217" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A217" t="s">
-        <v>39</v>
+        <v>54</v>
       </c>
       <c r="B217" s="2">
         <v>43755</v>
@@ -6989,7 +6992,7 @@
         <v>25</v>
       </c>
       <c r="F217" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="G217">
         <v>8.5</v>
@@ -7003,7 +7006,7 @@
     </row>
     <row r="218" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A218" t="s">
-        <v>39</v>
+        <v>54</v>
       </c>
       <c r="B218" s="2">
         <v>43759</v>
@@ -7018,7 +7021,7 @@
         <v>25</v>
       </c>
       <c r="F218" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="G218">
         <v>8.5</v>
@@ -7032,7 +7035,7 @@
     </row>
     <row r="219" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A219" t="s">
-        <v>39</v>
+        <v>54</v>
       </c>
       <c r="B219" s="2">
         <v>43762</v>
@@ -7047,7 +7050,7 @@
         <v>25</v>
       </c>
       <c r="F219" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="G219">
         <v>8.5</v>
@@ -7061,7 +7064,7 @@
     </row>
     <row r="220" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A220" t="s">
-        <v>39</v>
+        <v>54</v>
       </c>
       <c r="B220" s="2">
         <v>43767</v>
@@ -7076,7 +7079,7 @@
         <v>25</v>
       </c>
       <c r="F220" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="G220">
         <v>8.5</v>
@@ -7090,7 +7093,7 @@
     </row>
     <row r="221" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A221" t="s">
-        <v>39</v>
+        <v>54</v>
       </c>
       <c r="B221" s="2">
         <v>43769</v>
@@ -7105,7 +7108,7 @@
         <v>25</v>
       </c>
       <c r="F221" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="G221">
         <v>8.5</v>
@@ -7119,7 +7122,7 @@
     </row>
     <row r="222" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A222" t="s">
-        <v>39</v>
+        <v>54</v>
       </c>
       <c r="B222" s="2">
         <v>43773</v>
@@ -7134,7 +7137,7 @@
         <v>25</v>
       </c>
       <c r="F222" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="G222">
         <v>8.5</v>
@@ -7148,7 +7151,7 @@
     </row>
     <row r="223" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A223" t="s">
-        <v>39</v>
+        <v>54</v>
       </c>
       <c r="B223" s="2">
         <v>43776</v>
@@ -7163,7 +7166,7 @@
         <v>25</v>
       </c>
       <c r="F223" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="G223">
         <v>8.5</v>
@@ -7177,7 +7180,7 @@
     </row>
     <row r="224" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A224" t="s">
-        <v>39</v>
+        <v>54</v>
       </c>
       <c r="B224" s="2">
         <v>43780</v>
@@ -7192,7 +7195,7 @@
         <v>25</v>
       </c>
       <c r="F224" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="G224">
         <v>8.5</v>
@@ -7206,7 +7209,7 @@
     </row>
     <row r="225" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A225" t="s">
-        <v>39</v>
+        <v>54</v>
       </c>
       <c r="B225" s="2">
         <v>43787</v>
@@ -7221,7 +7224,7 @@
         <v>25</v>
       </c>
       <c r="F225" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="G225">
         <v>9</v>
@@ -7235,7 +7238,7 @@
     </row>
     <row r="226" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A226" t="s">
-        <v>39</v>
+        <v>54</v>
       </c>
       <c r="B226" s="2">
         <v>43794</v>
@@ -7250,7 +7253,7 @@
         <v>25</v>
       </c>
       <c r="F226" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="G226">
         <v>9</v>
@@ -7270,7 +7273,7 @@
     </row>
     <row r="227" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A227" t="s">
-        <v>41</v>
+        <v>55</v>
       </c>
       <c r="B227" s="2">
         <v>43720</v>
@@ -7285,7 +7288,7 @@
         <v>25</v>
       </c>
       <c r="F227" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="G227">
         <v>0</v>
@@ -7299,7 +7302,7 @@
     </row>
     <row r="228" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A228" t="s">
-        <v>41</v>
+        <v>55</v>
       </c>
       <c r="B228" s="2">
         <v>43724</v>
@@ -7314,7 +7317,7 @@
         <v>25</v>
       </c>
       <c r="F228" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="G228">
         <v>0</v>
@@ -7328,7 +7331,7 @@
     </row>
     <row r="229" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A229" t="s">
-        <v>41</v>
+        <v>55</v>
       </c>
       <c r="B229" s="2">
         <v>43727</v>
@@ -7343,7 +7346,7 @@
         <v>25</v>
       </c>
       <c r="F229" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="G229">
         <v>0</v>
@@ -7357,7 +7360,7 @@
     </row>
     <row r="230" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A230" t="s">
-        <v>41</v>
+        <v>55</v>
       </c>
       <c r="B230" s="2">
         <v>43731</v>
@@ -7372,7 +7375,7 @@
         <v>25</v>
       </c>
       <c r="F230" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="G230">
         <v>0</v>
@@ -7386,7 +7389,7 @@
     </row>
     <row r="231" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A231" t="s">
-        <v>41</v>
+        <v>55</v>
       </c>
       <c r="B231" s="2">
         <v>43734</v>
@@ -7401,7 +7404,7 @@
         <v>25</v>
       </c>
       <c r="F231" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="G231">
         <v>0</v>
@@ -7415,7 +7418,7 @@
     </row>
     <row r="232" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A232" t="s">
-        <v>41</v>
+        <v>55</v>
       </c>
       <c r="B232" s="2">
         <v>43738</v>
@@ -7430,7 +7433,7 @@
         <v>25</v>
       </c>
       <c r="F232" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="G232">
         <v>3.5</v>
@@ -7444,7 +7447,7 @@
     </row>
     <row r="233" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A233" t="s">
-        <v>41</v>
+        <v>55</v>
       </c>
       <c r="B233" s="2">
         <v>43741</v>
@@ -7459,7 +7462,7 @@
         <v>25</v>
       </c>
       <c r="F233" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="G233">
         <v>5.5</v>
@@ -7473,7 +7476,7 @@
     </row>
     <row r="234" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A234" t="s">
-        <v>41</v>
+        <v>55</v>
       </c>
       <c r="B234" s="2">
         <v>43745</v>
@@ -7488,7 +7491,7 @@
         <v>25</v>
       </c>
       <c r="F234" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="G234">
         <v>7</v>
@@ -7502,7 +7505,7 @@
     </row>
     <row r="235" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A235" t="s">
-        <v>41</v>
+        <v>55</v>
       </c>
       <c r="B235" s="2">
         <v>43748</v>
@@ -7517,7 +7520,7 @@
         <v>25</v>
       </c>
       <c r="F235" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="G235">
         <v>7</v>
@@ -7531,7 +7534,7 @@
     </row>
     <row r="236" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A236" t="s">
-        <v>41</v>
+        <v>55</v>
       </c>
       <c r="B236" s="2">
         <v>43752</v>
@@ -7546,7 +7549,7 @@
         <v>25</v>
       </c>
       <c r="F236" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="G236">
         <v>7</v>
@@ -7560,7 +7563,7 @@
     </row>
     <row r="237" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A237" t="s">
-        <v>41</v>
+        <v>55</v>
       </c>
       <c r="B237" s="2">
         <v>43755</v>
@@ -7575,7 +7578,7 @@
         <v>25</v>
       </c>
       <c r="F237" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="G237">
         <v>7</v>
@@ -7589,7 +7592,7 @@
     </row>
     <row r="238" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A238" t="s">
-        <v>41</v>
+        <v>55</v>
       </c>
       <c r="B238" s="2">
         <v>43759</v>
@@ -7604,7 +7607,7 @@
         <v>25</v>
       </c>
       <c r="F238" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="G238">
         <v>7</v>
@@ -7618,7 +7621,7 @@
     </row>
     <row r="239" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A239" t="s">
-        <v>41</v>
+        <v>55</v>
       </c>
       <c r="B239" s="2">
         <v>43762</v>
@@ -7633,7 +7636,7 @@
         <v>25</v>
       </c>
       <c r="F239" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="G239">
         <v>7</v>
@@ -7647,7 +7650,7 @@
     </row>
     <row r="240" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A240" t="s">
-        <v>41</v>
+        <v>55</v>
       </c>
       <c r="B240" s="2">
         <v>43767</v>
@@ -7662,7 +7665,7 @@
         <v>25</v>
       </c>
       <c r="F240" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="G240">
         <v>7</v>
@@ -7676,7 +7679,7 @@
     </row>
     <row r="241" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A241" t="s">
-        <v>41</v>
+        <v>55</v>
       </c>
       <c r="B241" s="2">
         <v>43769</v>
@@ -7691,7 +7694,7 @@
         <v>25</v>
       </c>
       <c r="F241" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="G241">
         <v>7</v>
@@ -7705,7 +7708,7 @@
     </row>
     <row r="242" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A242" t="s">
-        <v>41</v>
+        <v>55</v>
       </c>
       <c r="B242" s="2">
         <v>43773</v>
@@ -7720,7 +7723,7 @@
         <v>25</v>
       </c>
       <c r="F242" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="G242">
         <v>7</v>
@@ -7734,7 +7737,7 @@
     </row>
     <row r="243" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A243" t="s">
-        <v>41</v>
+        <v>55</v>
       </c>
       <c r="B243" s="2">
         <v>43776</v>
@@ -7749,7 +7752,7 @@
         <v>25</v>
       </c>
       <c r="F243" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="G243">
         <v>7</v>
@@ -7763,7 +7766,7 @@
     </row>
     <row r="244" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A244" t="s">
-        <v>41</v>
+        <v>55</v>
       </c>
       <c r="B244" s="2">
         <v>43780</v>
@@ -7778,7 +7781,7 @@
         <v>25</v>
       </c>
       <c r="F244" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="G244">
         <v>7</v>
@@ -7792,7 +7795,7 @@
     </row>
     <row r="245" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A245" t="s">
-        <v>41</v>
+        <v>55</v>
       </c>
       <c r="B245" s="2">
         <v>43787</v>
@@ -7807,7 +7810,7 @@
         <v>25</v>
       </c>
       <c r="F245" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="G245">
         <v>7</v>
@@ -7821,7 +7824,7 @@
     </row>
     <row r="246" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A246" t="s">
-        <v>41</v>
+        <v>55</v>
       </c>
       <c r="B246" s="2">
         <v>43794</v>
@@ -7836,7 +7839,7 @@
         <v>25</v>
       </c>
       <c r="F246" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="G246">
         <v>7</v>
@@ -7856,7 +7859,7 @@
     </row>
     <row r="247" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A247" t="s">
-        <v>42</v>
+        <v>56</v>
       </c>
       <c r="B247" s="2">
         <v>44089</v>
@@ -7871,7 +7874,7 @@
         <v>25</v>
       </c>
       <c r="F247" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="G247">
         <v>0</v>
@@ -7885,7 +7888,7 @@
     </row>
     <row r="248" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A248" t="s">
-        <v>42</v>
+        <v>56</v>
       </c>
       <c r="B248" s="2">
         <v>44091</v>
@@ -7900,7 +7903,7 @@
         <v>25</v>
       </c>
       <c r="F248" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="G248">
         <v>0</v>
@@ -7914,7 +7917,7 @@
     </row>
     <row r="249" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A249" t="s">
-        <v>42</v>
+        <v>56</v>
       </c>
       <c r="B249" s="2">
         <v>44095</v>
@@ -7929,7 +7932,7 @@
         <v>25</v>
       </c>
       <c r="F249" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="G249">
         <v>0</v>
@@ -7943,7 +7946,7 @@
     </row>
     <row r="250" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A250" t="s">
-        <v>42</v>
+        <v>56</v>
       </c>
       <c r="B250" s="2">
         <v>44097</v>
@@ -7958,7 +7961,7 @@
         <v>25</v>
       </c>
       <c r="F250" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="G250">
         <v>0</v>
@@ -7972,7 +7975,7 @@
     </row>
     <row r="251" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A251" t="s">
-        <v>42</v>
+        <v>56</v>
       </c>
       <c r="B251" s="2">
         <v>44102</v>
@@ -7987,7 +7990,7 @@
         <v>25</v>
       </c>
       <c r="F251" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="G251">
         <v>2</v>
@@ -8001,7 +8004,7 @@
     </row>
     <row r="252" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A252" t="s">
-        <v>42</v>
+        <v>56</v>
       </c>
       <c r="B252" s="2">
         <v>44105</v>
@@ -8016,7 +8019,7 @@
         <v>25</v>
       </c>
       <c r="F252" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="G252">
         <v>2</v>
@@ -8030,7 +8033,7 @@
     </row>
     <row r="253" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A253" t="s">
-        <v>42</v>
+        <v>56</v>
       </c>
       <c r="B253" s="2">
         <v>44110</v>
@@ -8045,7 +8048,7 @@
         <v>25</v>
       </c>
       <c r="F253" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="G253">
         <v>4</v>
@@ -8059,7 +8062,7 @@
     </row>
     <row r="254" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A254" t="s">
-        <v>42</v>
+        <v>56</v>
       </c>
       <c r="B254" s="2">
         <v>44113</v>
@@ -8074,7 +8077,7 @@
         <v>25</v>
       </c>
       <c r="F254" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="G254">
         <v>4</v>
@@ -8088,7 +8091,7 @@
     </row>
     <row r="255" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A255" t="s">
-        <v>42</v>
+        <v>56</v>
       </c>
       <c r="B255" s="2">
         <v>44118</v>
@@ -8103,7 +8106,7 @@
         <v>25</v>
       </c>
       <c r="F255" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="G255">
         <v>5</v>
@@ -8117,7 +8120,7 @@
     </row>
     <row r="256" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A256" t="s">
-        <v>42</v>
+        <v>56</v>
       </c>
       <c r="B256" s="2">
         <v>44123</v>
@@ -8132,7 +8135,7 @@
         <v>25</v>
       </c>
       <c r="F256" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="G256">
         <v>5</v>
@@ -8146,7 +8149,7 @@
     </row>
     <row r="257" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A257" t="s">
-        <v>42</v>
+        <v>56</v>
       </c>
       <c r="B257" s="2">
         <v>44131</v>
@@ -8161,7 +8164,7 @@
         <v>25</v>
       </c>
       <c r="F257" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="G257">
         <v>5</v>
@@ -8175,7 +8178,7 @@
     </row>
     <row r="258" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A258" t="s">
-        <v>42</v>
+        <v>56</v>
       </c>
       <c r="B258" s="2">
         <v>44134</v>
@@ -8190,7 +8193,7 @@
         <v>25</v>
       </c>
       <c r="F258" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="G258">
         <v>5</v>
@@ -8204,7 +8207,7 @@
     </row>
     <row r="259" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A259" t="s">
-        <v>42</v>
+        <v>56</v>
       </c>
       <c r="B259" s="2">
         <v>44137</v>
@@ -8219,7 +8222,7 @@
         <v>25</v>
       </c>
       <c r="F259" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="G259">
         <v>5</v>
@@ -8233,7 +8236,7 @@
     </row>
     <row r="260" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A260" t="s">
-        <v>42</v>
+        <v>56</v>
       </c>
       <c r="B260" s="2">
         <v>44144</v>
@@ -8248,7 +8251,7 @@
         <v>25</v>
       </c>
       <c r="F260" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="G260">
         <v>5</v>
@@ -8262,7 +8265,7 @@
     </row>
     <row r="261" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A261" t="s">
-        <v>42</v>
+        <v>56</v>
       </c>
       <c r="B261" s="2">
         <v>44152</v>
@@ -8277,7 +8280,7 @@
         <v>25</v>
       </c>
       <c r="F261" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="G261">
         <v>5</v>
@@ -8291,7 +8294,7 @@
     </row>
     <row r="262" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A262" t="s">
-        <v>42</v>
+        <v>56</v>
       </c>
       <c r="B262" s="2">
         <v>44155</v>
@@ -8306,7 +8309,7 @@
         <v>25</v>
       </c>
       <c r="F262" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="G262">
         <v>5</v>
@@ -8326,7 +8329,7 @@
     </row>
     <row r="263" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A263" t="s">
-        <v>44</v>
+        <v>57</v>
       </c>
       <c r="B263" s="2">
         <v>44089</v>
@@ -8341,7 +8344,7 @@
         <v>25</v>
       </c>
       <c r="F263" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="G263">
         <v>0</v>
@@ -8355,7 +8358,7 @@
     </row>
     <row r="264" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A264" t="s">
-        <v>44</v>
+        <v>57</v>
       </c>
       <c r="B264" s="2">
         <v>44091</v>
@@ -8370,7 +8373,7 @@
         <v>25</v>
       </c>
       <c r="F264" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="G264">
         <v>0</v>
@@ -8384,7 +8387,7 @@
     </row>
     <row r="265" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A265" t="s">
-        <v>44</v>
+        <v>57</v>
       </c>
       <c r="B265" s="2">
         <v>44095</v>
@@ -8399,7 +8402,7 @@
         <v>25</v>
       </c>
       <c r="F265" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="G265">
         <v>1</v>
@@ -8413,7 +8416,7 @@
     </row>
     <row r="266" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A266" t="s">
-        <v>44</v>
+        <v>57</v>
       </c>
       <c r="B266" s="2">
         <v>44097</v>
@@ -8428,7 +8431,7 @@
         <v>25</v>
       </c>
       <c r="F266" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="G266">
         <v>2</v>
@@ -8442,7 +8445,7 @@
     </row>
     <row r="267" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A267" t="s">
-        <v>44</v>
+        <v>57</v>
       </c>
       <c r="B267" s="2">
         <v>44102</v>
@@ -8457,7 +8460,7 @@
         <v>25</v>
       </c>
       <c r="F267" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="G267">
         <v>5</v>
@@ -8471,7 +8474,7 @@
     </row>
     <row r="268" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A268" t="s">
-        <v>44</v>
+        <v>57</v>
       </c>
       <c r="B268" s="2">
         <v>44105</v>
@@ -8486,7 +8489,7 @@
         <v>25</v>
       </c>
       <c r="F268" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="G268">
         <v>5</v>
@@ -8500,7 +8503,7 @@
     </row>
     <row r="269" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A269" t="s">
-        <v>44</v>
+        <v>57</v>
       </c>
       <c r="B269" s="2">
         <v>44110</v>
@@ -8515,7 +8518,7 @@
         <v>25</v>
       </c>
       <c r="F269" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="G269">
         <v>5</v>
@@ -8529,7 +8532,7 @@
     </row>
     <row r="270" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A270" t="s">
-        <v>44</v>
+        <v>57</v>
       </c>
       <c r="B270" s="2">
         <v>44113</v>
@@ -8544,7 +8547,7 @@
         <v>25</v>
       </c>
       <c r="F270" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="G270">
         <v>5</v>
@@ -8558,7 +8561,7 @@
     </row>
     <row r="271" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A271" t="s">
-        <v>44</v>
+        <v>57</v>
       </c>
       <c r="B271" s="2">
         <v>44118</v>
@@ -8573,7 +8576,7 @@
         <v>25</v>
       </c>
       <c r="F271" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="G271">
         <v>5</v>
@@ -8587,7 +8590,7 @@
     </row>
     <row r="272" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A272" t="s">
-        <v>44</v>
+        <v>57</v>
       </c>
       <c r="B272" s="2">
         <v>44123</v>
@@ -8602,7 +8605,7 @@
         <v>25</v>
       </c>
       <c r="F272" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="G272">
         <v>5</v>
@@ -8616,7 +8619,7 @@
     </row>
     <row r="273" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A273" t="s">
-        <v>44</v>
+        <v>57</v>
       </c>
       <c r="B273" s="2">
         <v>44131</v>
@@ -8631,7 +8634,7 @@
         <v>25</v>
       </c>
       <c r="F273" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="G273">
         <v>5</v>
@@ -8645,7 +8648,7 @@
     </row>
     <row r="274" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A274" t="s">
-        <v>44</v>
+        <v>57</v>
       </c>
       <c r="B274" s="2">
         <v>44134</v>
@@ -8660,7 +8663,7 @@
         <v>25</v>
       </c>
       <c r="F274" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="G274">
         <v>5</v>
@@ -8674,7 +8677,7 @@
     </row>
     <row r="275" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A275" t="s">
-        <v>44</v>
+        <v>57</v>
       </c>
       <c r="B275" s="2">
         <v>44137</v>
@@ -8689,7 +8692,7 @@
         <v>25</v>
       </c>
       <c r="F275" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="G275">
         <v>5</v>
@@ -8703,7 +8706,7 @@
     </row>
     <row r="276" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A276" t="s">
-        <v>44</v>
+        <v>57</v>
       </c>
       <c r="B276" s="2">
         <v>44144</v>
@@ -8718,7 +8721,7 @@
         <v>25</v>
       </c>
       <c r="F276" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="G276">
         <v>5</v>
@@ -8732,7 +8735,7 @@
     </row>
     <row r="277" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A277" t="s">
-        <v>44</v>
+        <v>57</v>
       </c>
       <c r="B277" s="2">
         <v>44152</v>
@@ -8747,7 +8750,7 @@
         <v>25</v>
       </c>
       <c r="F277" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="G277">
         <v>5</v>
@@ -8761,7 +8764,7 @@
     </row>
     <row r="278" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A278" t="s">
-        <v>44</v>
+        <v>57</v>
       </c>
       <c r="B278" s="2">
         <v>44155</v>
@@ -8776,7 +8779,7 @@
         <v>25</v>
       </c>
       <c r="F278" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="G278">
         <v>5</v>
@@ -8796,7 +8799,7 @@
     </row>
     <row r="279" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A279" t="s">
-        <v>45</v>
+        <v>58</v>
       </c>
       <c r="B279" s="2">
         <v>44089</v>
@@ -8811,7 +8814,7 @@
         <v>25</v>
       </c>
       <c r="F279" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="G279">
         <v>0</v>
@@ -8825,7 +8828,7 @@
     </row>
     <row r="280" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A280" t="s">
-        <v>45</v>
+        <v>58</v>
       </c>
       <c r="B280" s="2">
         <v>44091</v>
@@ -8840,7 +8843,7 @@
         <v>25</v>
       </c>
       <c r="F280" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="G280">
         <v>0</v>
@@ -8854,7 +8857,7 @@
     </row>
     <row r="281" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A281" t="s">
-        <v>45</v>
+        <v>58</v>
       </c>
       <c r="B281" s="2">
         <v>44095</v>
@@ -8869,7 +8872,7 @@
         <v>25</v>
       </c>
       <c r="F281" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="G281">
         <v>0</v>
@@ -8883,7 +8886,7 @@
     </row>
     <row r="282" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A282" t="s">
-        <v>45</v>
+        <v>58</v>
       </c>
       <c r="B282" s="2">
         <v>44097</v>
@@ -8898,7 +8901,7 @@
         <v>25</v>
       </c>
       <c r="F282" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="G282">
         <v>0</v>
@@ -8912,7 +8915,7 @@
     </row>
     <row r="283" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A283" t="s">
-        <v>45</v>
+        <v>58</v>
       </c>
       <c r="B283" s="2">
         <v>44102</v>
@@ -8927,7 +8930,7 @@
         <v>25</v>
       </c>
       <c r="F283" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="G283">
         <v>0</v>
@@ -8941,7 +8944,7 @@
     </row>
     <row r="284" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A284" t="s">
-        <v>45</v>
+        <v>58</v>
       </c>
       <c r="B284" s="2">
         <v>44105</v>
@@ -8956,7 +8959,7 @@
         <v>25</v>
       </c>
       <c r="F284" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="G284">
         <v>1</v>
@@ -8970,7 +8973,7 @@
     </row>
     <row r="285" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A285" t="s">
-        <v>45</v>
+        <v>58</v>
       </c>
       <c r="B285" s="2">
         <v>44110</v>
@@ -8985,7 +8988,7 @@
         <v>25</v>
       </c>
       <c r="F285" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="G285">
         <v>4</v>
@@ -8999,7 +9002,7 @@
     </row>
     <row r="286" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A286" t="s">
-        <v>45</v>
+        <v>58</v>
       </c>
       <c r="B286" s="2">
         <v>44113</v>
@@ -9014,7 +9017,7 @@
         <v>25</v>
       </c>
       <c r="F286" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="G286">
         <v>6</v>
@@ -9028,7 +9031,7 @@
     </row>
     <row r="287" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A287" t="s">
-        <v>45</v>
+        <v>58</v>
       </c>
       <c r="B287" s="2">
         <v>44118</v>
@@ -9043,7 +9046,7 @@
         <v>25</v>
       </c>
       <c r="F287" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="G287">
         <v>7</v>
@@ -9057,7 +9060,7 @@
     </row>
     <row r="288" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A288" t="s">
-        <v>45</v>
+        <v>58</v>
       </c>
       <c r="B288" s="2">
         <v>44123</v>
@@ -9072,7 +9075,7 @@
         <v>25</v>
       </c>
       <c r="F288" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="G288">
         <v>7</v>
@@ -9086,7 +9089,7 @@
     </row>
     <row r="289" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A289" t="s">
-        <v>45</v>
+        <v>58</v>
       </c>
       <c r="B289" s="2">
         <v>44131</v>
@@ -9101,7 +9104,7 @@
         <v>25</v>
       </c>
       <c r="F289" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="G289">
         <v>7</v>
@@ -9115,7 +9118,7 @@
     </row>
     <row r="290" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A290" t="s">
-        <v>45</v>
+        <v>58</v>
       </c>
       <c r="B290" s="2">
         <v>44134</v>
@@ -9130,7 +9133,7 @@
         <v>25</v>
       </c>
       <c r="F290" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="G290">
         <v>7</v>
@@ -9144,7 +9147,7 @@
     </row>
     <row r="291" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A291" t="s">
-        <v>45</v>
+        <v>58</v>
       </c>
       <c r="B291" s="2">
         <v>44137</v>
@@ -9159,7 +9162,7 @@
         <v>25</v>
       </c>
       <c r="F291" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="G291">
         <v>7</v>
@@ -9173,7 +9176,7 @@
     </row>
     <row r="292" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A292" t="s">
-        <v>45</v>
+        <v>58</v>
       </c>
       <c r="B292" s="2">
         <v>44144</v>
@@ -9188,7 +9191,7 @@
         <v>25</v>
       </c>
       <c r="F292" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="G292">
         <v>7</v>
@@ -9202,7 +9205,7 @@
     </row>
     <row r="293" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A293" t="s">
-        <v>45</v>
+        <v>58</v>
       </c>
       <c r="B293" s="2">
         <v>44152</v>
@@ -9217,7 +9220,7 @@
         <v>25</v>
       </c>
       <c r="F293" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="G293">
         <v>7</v>
@@ -9231,7 +9234,7 @@
     </row>
     <row r="294" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A294" t="s">
-        <v>45</v>
+        <v>58</v>
       </c>
       <c r="B294" s="2">
         <v>44155</v>
@@ -9246,7 +9249,7 @@
         <v>25</v>
       </c>
       <c r="F294" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="G294">
         <v>7</v>
@@ -9266,7 +9269,7 @@
     </row>
     <row r="295" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A295" t="s">
-        <v>46</v>
+        <v>59</v>
       </c>
       <c r="B295" s="2">
         <v>44095</v>
@@ -9281,7 +9284,7 @@
         <v>25</v>
       </c>
       <c r="F295" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="G295">
         <v>0</v>
@@ -9295,7 +9298,7 @@
     </row>
     <row r="296" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A296" t="s">
-        <v>46</v>
+        <v>59</v>
       </c>
       <c r="B296" s="2">
         <v>44098</v>
@@ -9310,7 +9313,7 @@
         <v>25</v>
       </c>
       <c r="F296" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="G296">
         <v>0</v>
@@ -9324,7 +9327,7 @@
     </row>
     <row r="297" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A297" t="s">
-        <v>46</v>
+        <v>59</v>
       </c>
       <c r="B297" s="2">
         <v>44103</v>
@@ -9339,7 +9342,7 @@
         <v>25</v>
       </c>
       <c r="F297" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="G297">
         <v>0.5</v>
@@ -9353,7 +9356,7 @@
     </row>
     <row r="298" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A298" t="s">
-        <v>46</v>
+        <v>59</v>
       </c>
       <c r="B298" s="2">
         <v>44106</v>
@@ -9368,7 +9371,7 @@
         <v>25</v>
       </c>
       <c r="F298" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="G298">
         <v>1</v>
@@ -9382,7 +9385,7 @@
     </row>
     <row r="299" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A299" t="s">
-        <v>46</v>
+        <v>59</v>
       </c>
       <c r="B299" s="2">
         <v>44110</v>
@@ -9397,7 +9400,7 @@
         <v>25</v>
       </c>
       <c r="F299" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="G299">
         <v>3</v>
@@ -9411,7 +9414,7 @@
     </row>
     <row r="300" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A300" t="s">
-        <v>46</v>
+        <v>59</v>
       </c>
       <c r="B300" s="2">
         <v>44118</v>
@@ -9426,7 +9429,7 @@
         <v>25</v>
       </c>
       <c r="F300" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="G300">
         <v>5</v>
@@ -9440,7 +9443,7 @@
     </row>
     <row r="301" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A301" t="s">
-        <v>46</v>
+        <v>59</v>
       </c>
       <c r="B301" s="2">
         <v>44123</v>
@@ -9455,7 +9458,7 @@
         <v>25</v>
       </c>
       <c r="F301" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="G301">
         <v>5</v>
@@ -9469,7 +9472,7 @@
     </row>
     <row r="302" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A302" t="s">
-        <v>46</v>
+        <v>59</v>
       </c>
       <c r="B302" s="2">
         <v>44132</v>
@@ -9484,7 +9487,7 @@
         <v>25</v>
       </c>
       <c r="F302" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="G302">
         <v>5</v>
@@ -9498,7 +9501,7 @@
     </row>
     <row r="303" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A303" t="s">
-        <v>46</v>
+        <v>59</v>
       </c>
       <c r="B303" s="2">
         <v>44134</v>
@@ -9513,7 +9516,7 @@
         <v>25</v>
       </c>
       <c r="F303" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="G303">
         <v>5</v>
@@ -9527,7 +9530,7 @@
     </row>
     <row r="304" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A304" t="s">
-        <v>46</v>
+        <v>59</v>
       </c>
       <c r="B304" s="2">
         <v>44138</v>
@@ -9542,7 +9545,7 @@
         <v>25</v>
       </c>
       <c r="F304" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="G304">
         <v>5</v>
@@ -9556,7 +9559,7 @@
     </row>
     <row r="305" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A305" t="s">
-        <v>46</v>
+        <v>59</v>
       </c>
       <c r="B305" s="2">
         <v>44144</v>
@@ -9571,7 +9574,7 @@
         <v>25</v>
       </c>
       <c r="F305" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="G305">
         <v>5</v>
@@ -9585,7 +9588,7 @@
     </row>
     <row r="306" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A306" t="s">
-        <v>46</v>
+        <v>59</v>
       </c>
       <c r="B306" s="2">
         <v>44152</v>
@@ -9600,7 +9603,7 @@
         <v>25</v>
       </c>
       <c r="F306" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="G306">
         <v>5</v>
@@ -9620,7 +9623,7 @@
     </row>
     <row r="307" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A307" t="s">
-        <v>47</v>
+        <v>60</v>
       </c>
       <c r="B307" s="2">
         <v>44095</v>
@@ -9635,7 +9638,7 @@
         <v>25</v>
       </c>
       <c r="F307" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="G307">
         <v>0</v>
@@ -9649,7 +9652,7 @@
     </row>
     <row r="308" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A308" t="s">
-        <v>47</v>
+        <v>60</v>
       </c>
       <c r="B308" s="2">
         <v>44098</v>
@@ -9664,7 +9667,7 @@
         <v>25</v>
       </c>
       <c r="F308" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="G308">
         <v>0.5</v>
@@ -9678,7 +9681,7 @@
     </row>
     <row r="309" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A309" t="s">
-        <v>47</v>
+        <v>60</v>
       </c>
       <c r="B309" s="2">
         <v>44103</v>
@@ -9693,7 +9696,7 @@
         <v>25</v>
       </c>
       <c r="F309" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="G309">
         <v>2</v>
@@ -9707,7 +9710,7 @@
     </row>
     <row r="310" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A310" t="s">
-        <v>47</v>
+        <v>60</v>
       </c>
       <c r="B310" s="2">
         <v>44106</v>
@@ -9722,7 +9725,7 @@
         <v>25</v>
       </c>
       <c r="F310" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="G310">
         <v>2</v>
@@ -9736,7 +9739,7 @@
     </row>
     <row r="311" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A311" t="s">
-        <v>47</v>
+        <v>60</v>
       </c>
       <c r="B311" s="2">
         <v>44110</v>
@@ -9751,7 +9754,7 @@
         <v>25</v>
       </c>
       <c r="F311" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="G311">
         <v>3</v>
@@ -9765,7 +9768,7 @@
     </row>
     <row r="312" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A312" t="s">
-        <v>47</v>
+        <v>60</v>
       </c>
       <c r="B312" s="2">
         <v>44118</v>
@@ -9780,7 +9783,7 @@
         <v>25</v>
       </c>
       <c r="F312" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="G312">
         <v>3</v>
@@ -9794,7 +9797,7 @@
     </row>
     <row r="313" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A313" t="s">
-        <v>47</v>
+        <v>60</v>
       </c>
       <c r="B313" s="2">
         <v>44123</v>
@@ -9809,7 +9812,7 @@
         <v>25</v>
       </c>
       <c r="F313" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="G313">
         <v>3</v>
@@ -9823,7 +9826,7 @@
     </row>
     <row r="314" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A314" t="s">
-        <v>47</v>
+        <v>60</v>
       </c>
       <c r="B314" s="2">
         <v>44132</v>
@@ -9838,7 +9841,7 @@
         <v>25</v>
       </c>
       <c r="F314" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="G314">
         <v>4</v>
@@ -9852,7 +9855,7 @@
     </row>
     <row r="315" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A315" t="s">
-        <v>47</v>
+        <v>60</v>
       </c>
       <c r="B315" s="2">
         <v>44134</v>
@@ -9867,7 +9870,7 @@
         <v>25</v>
       </c>
       <c r="F315" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="G315">
         <v>4</v>
@@ -9881,7 +9884,7 @@
     </row>
     <row r="316" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A316" t="s">
-        <v>47</v>
+        <v>60</v>
       </c>
       <c r="B316" s="2">
         <v>44138</v>
@@ -9896,7 +9899,7 @@
         <v>25</v>
       </c>
       <c r="F316" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="G316">
         <v>4</v>
@@ -9910,7 +9913,7 @@
     </row>
     <row r="317" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A317" t="s">
-        <v>47</v>
+        <v>60</v>
       </c>
       <c r="B317" s="2">
         <v>44144</v>
@@ -9925,7 +9928,7 @@
         <v>25</v>
       </c>
       <c r="F317" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="G317">
         <v>4</v>
@@ -9939,7 +9942,7 @@
     </row>
     <row r="318" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A318" t="s">
-        <v>47</v>
+        <v>60</v>
       </c>
       <c r="B318" s="2">
         <v>44152</v>
@@ -9954,7 +9957,7 @@
         <v>25</v>
       </c>
       <c r="F318" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="G318">
         <v>4</v>
@@ -9974,7 +9977,7 @@
     </row>
     <row r="319" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A319" t="s">
-        <v>48</v>
+        <v>61</v>
       </c>
       <c r="B319" s="2">
         <v>44095</v>
@@ -9989,7 +9992,7 @@
         <v>25</v>
       </c>
       <c r="F319" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="G319">
         <v>0</v>
@@ -10003,7 +10006,7 @@
     </row>
     <row r="320" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A320" t="s">
-        <v>48</v>
+        <v>61</v>
       </c>
       <c r="B320" s="2">
         <v>44098</v>
@@ -10018,7 +10021,7 @@
         <v>25</v>
       </c>
       <c r="F320" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="G320">
         <v>0</v>
@@ -10032,7 +10035,7 @@
     </row>
     <row r="321" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A321" t="s">
-        <v>48</v>
+        <v>61</v>
       </c>
       <c r="B321" s="2">
         <v>44103</v>
@@ -10047,7 +10050,7 @@
         <v>25</v>
       </c>
       <c r="F321" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="G321">
         <v>1</v>
@@ -10061,7 +10064,7 @@
     </row>
     <row r="322" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A322" t="s">
-        <v>48</v>
+        <v>61</v>
       </c>
       <c r="B322" s="2">
         <v>44106</v>
@@ -10076,7 +10079,7 @@
         <v>25</v>
       </c>
       <c r="F322" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="G322">
         <v>1.5</v>
@@ -10090,7 +10093,7 @@
     </row>
     <row r="323" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A323" t="s">
-        <v>48</v>
+        <v>61</v>
       </c>
       <c r="B323" s="2">
         <v>44110</v>
@@ -10105,7 +10108,7 @@
         <v>25</v>
       </c>
       <c r="F323" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="G323">
         <v>4</v>
@@ -10119,7 +10122,7 @@
     </row>
     <row r="324" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A324" t="s">
-        <v>48</v>
+        <v>61</v>
       </c>
       <c r="B324" s="2">
         <v>44118</v>
@@ -10134,7 +10137,7 @@
         <v>25</v>
       </c>
       <c r="F324" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="G324">
         <v>4</v>
@@ -10148,7 +10151,7 @@
     </row>
     <row r="325" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A325" t="s">
-        <v>48</v>
+        <v>61</v>
       </c>
       <c r="B325" s="2">
         <v>44123</v>
@@ -10163,7 +10166,7 @@
         <v>25</v>
       </c>
       <c r="F325" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="G325">
         <v>4</v>
@@ -10177,7 +10180,7 @@
     </row>
     <row r="326" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A326" t="s">
-        <v>48</v>
+        <v>61</v>
       </c>
       <c r="B326" s="2">
         <v>44132</v>
@@ -10192,7 +10195,7 @@
         <v>25</v>
       </c>
       <c r="F326" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="G326">
         <v>5</v>
@@ -10206,7 +10209,7 @@
     </row>
     <row r="327" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A327" t="s">
-        <v>48</v>
+        <v>61</v>
       </c>
       <c r="B327" s="2">
         <v>44134</v>
@@ -10221,7 +10224,7 @@
         <v>25</v>
       </c>
       <c r="F327" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="G327">
         <v>5</v>
@@ -10235,7 +10238,7 @@
     </row>
     <row r="328" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A328" t="s">
-        <v>48</v>
+        <v>61</v>
       </c>
       <c r="B328" s="2">
         <v>44138</v>
@@ -10250,7 +10253,7 @@
         <v>25</v>
       </c>
       <c r="F328" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="G328">
         <v>5</v>
@@ -10264,7 +10267,7 @@
     </row>
     <row r="329" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A329" t="s">
-        <v>48</v>
+        <v>61</v>
       </c>
       <c r="B329" s="2">
         <v>44144</v>
@@ -10279,7 +10282,7 @@
         <v>25</v>
       </c>
       <c r="F329" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="G329">
         <v>5</v>
@@ -10293,7 +10296,7 @@
     </row>
     <row r="330" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A330" t="s">
-        <v>48</v>
+        <v>61</v>
       </c>
       <c r="B330" s="2">
         <v>44152</v>
@@ -10308,7 +10311,7 @@
         <v>25</v>
       </c>
       <c r="F330" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="G330">
         <v>5</v>
@@ -10328,7 +10331,7 @@
     </row>
     <row r="331" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A331" t="s">
-        <v>49</v>
+        <v>39</v>
       </c>
       <c r="B331" s="2">
         <v>44084</v>
@@ -10357,7 +10360,7 @@
     </row>
     <row r="332" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A332" t="s">
-        <v>49</v>
+        <v>39</v>
       </c>
       <c r="B332" s="2">
         <v>44088</v>
@@ -10386,7 +10389,7 @@
     </row>
     <row r="333" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A333" t="s">
-        <v>49</v>
+        <v>39</v>
       </c>
       <c r="B333" s="2">
         <v>44090</v>
@@ -10415,7 +10418,7 @@
     </row>
     <row r="334" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A334" t="s">
-        <v>49</v>
+        <v>39</v>
       </c>
       <c r="B334" s="2">
         <v>44092</v>
@@ -10444,7 +10447,7 @@
     </row>
     <row r="335" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A335" t="s">
-        <v>49</v>
+        <v>39</v>
       </c>
       <c r="B335" s="2">
         <v>44095</v>
@@ -10473,7 +10476,7 @@
     </row>
     <row r="336" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A336" t="s">
-        <v>49</v>
+        <v>39</v>
       </c>
       <c r="B336" s="2">
         <v>44097</v>
@@ -10502,7 +10505,7 @@
     </row>
     <row r="337" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A337" t="s">
-        <v>49</v>
+        <v>39</v>
       </c>
       <c r="B337" s="2">
         <v>44099</v>
@@ -10531,7 +10534,7 @@
     </row>
     <row r="338" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A338" t="s">
-        <v>49</v>
+        <v>39</v>
       </c>
       <c r="B338" s="2">
         <v>44102</v>
@@ -10560,7 +10563,7 @@
     </row>
     <row r="339" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A339" t="s">
-        <v>49</v>
+        <v>39</v>
       </c>
       <c r="B339" s="2">
         <v>44104</v>
@@ -10589,7 +10592,7 @@
     </row>
     <row r="340" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A340" t="s">
-        <v>49</v>
+        <v>39</v>
       </c>
       <c r="B340" s="2">
         <v>44106</v>
@@ -10618,7 +10621,7 @@
     </row>
     <row r="341" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A341" t="s">
-        <v>49</v>
+        <v>39</v>
       </c>
       <c r="B341" s="2">
         <v>44109</v>
@@ -10647,7 +10650,7 @@
     </row>
     <row r="342" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A342" t="s">
-        <v>49</v>
+        <v>39</v>
       </c>
       <c r="B342" s="2">
         <v>44111</v>
@@ -10676,7 +10679,7 @@
     </row>
     <row r="343" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A343" t="s">
-        <v>49</v>
+        <v>39</v>
       </c>
       <c r="B343" s="2">
         <v>44113</v>
@@ -10705,7 +10708,7 @@
     </row>
     <row r="344" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A344" t="s">
-        <v>49</v>
+        <v>39</v>
       </c>
       <c r="B344" s="2">
         <v>44116</v>
@@ -10734,7 +10737,7 @@
     </row>
     <row r="345" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A345" t="s">
-        <v>49</v>
+        <v>39</v>
       </c>
       <c r="B345" s="2">
         <v>44118</v>
@@ -10763,7 +10766,7 @@
     </row>
     <row r="346" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A346" t="s">
-        <v>49</v>
+        <v>39</v>
       </c>
       <c r="B346" s="2">
         <v>44120</v>
@@ -10792,7 +10795,7 @@
     </row>
     <row r="347" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A347" t="s">
-        <v>49</v>
+        <v>39</v>
       </c>
       <c r="B347" s="2">
         <v>44123</v>
@@ -10821,7 +10824,7 @@
     </row>
     <row r="348" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A348" t="s">
-        <v>49</v>
+        <v>39</v>
       </c>
       <c r="B348" s="2">
         <v>44125</v>
@@ -10850,7 +10853,7 @@
     </row>
     <row r="349" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A349" t="s">
-        <v>49</v>
+        <v>39</v>
       </c>
       <c r="B349" s="2">
         <v>44127</v>
@@ -10879,7 +10882,7 @@
     </row>
     <row r="350" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A350" t="s">
-        <v>49</v>
+        <v>39</v>
       </c>
       <c r="B350" s="2">
         <v>44131</v>
@@ -10914,7 +10917,7 @@
     </row>
     <row r="351" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A351" t="s">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="B351" s="2">
         <v>44084</v>
@@ -10943,7 +10946,7 @@
     </row>
     <row r="352" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A352" t="s">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="B352" s="2">
         <v>44088</v>
@@ -10972,7 +10975,7 @@
     </row>
     <row r="353" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A353" t="s">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="B353" s="2">
         <v>44090</v>
@@ -11001,7 +11004,7 @@
     </row>
     <row r="354" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A354" t="s">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="B354" s="2">
         <v>44092</v>
@@ -11030,7 +11033,7 @@
     </row>
     <row r="355" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A355" t="s">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="B355" s="2">
         <v>44095</v>
@@ -11059,7 +11062,7 @@
     </row>
     <row r="356" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A356" t="s">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="B356" s="2">
         <v>44097</v>
@@ -11088,7 +11091,7 @@
     </row>
     <row r="357" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A357" t="s">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="B357" s="2">
         <v>44099</v>
@@ -11117,7 +11120,7 @@
     </row>
     <row r="358" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A358" t="s">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="B358" s="2">
         <v>44102</v>
@@ -11146,7 +11149,7 @@
     </row>
     <row r="359" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A359" t="s">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="B359" s="2">
         <v>44104</v>
@@ -11175,7 +11178,7 @@
     </row>
     <row r="360" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A360" t="s">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="B360" s="2">
         <v>44106</v>
@@ -11204,7 +11207,7 @@
     </row>
     <row r="361" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A361" t="s">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="B361" s="2">
         <v>44109</v>
@@ -11233,7 +11236,7 @@
     </row>
     <row r="362" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A362" t="s">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="B362" s="2">
         <v>44111</v>
@@ -11262,7 +11265,7 @@
     </row>
     <row r="363" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A363" t="s">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="B363" s="2">
         <v>44113</v>
@@ -11291,7 +11294,7 @@
     </row>
     <row r="364" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A364" t="s">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="B364" s="2">
         <v>44116</v>
@@ -11320,7 +11323,7 @@
     </row>
     <row r="365" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A365" t="s">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="B365" s="2">
         <v>44118</v>
@@ -11349,7 +11352,7 @@
     </row>
     <row r="366" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A366" t="s">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="B366" s="2">
         <v>44120</v>
@@ -11378,7 +11381,7 @@
     </row>
     <row r="367" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A367" t="s">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="B367" s="2">
         <v>44123</v>
@@ -11407,7 +11410,7 @@
     </row>
     <row r="368" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A368" t="s">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="B368" s="2">
         <v>44125</v>
@@ -11436,7 +11439,7 @@
     </row>
     <row r="369" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A369" t="s">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="B369" s="2">
         <v>44127</v>
@@ -11465,7 +11468,7 @@
     </row>
     <row r="370" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A370" t="s">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="B370" s="2">
         <v>44131</v>
@@ -11500,7 +11503,7 @@
     </row>
     <row r="371" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A371" t="s">
-        <v>51</v>
+        <v>41</v>
       </c>
       <c r="B371" s="2">
         <v>44084</v>
@@ -11529,7 +11532,7 @@
     </row>
     <row r="372" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A372" t="s">
-        <v>51</v>
+        <v>41</v>
       </c>
       <c r="B372" s="2">
         <v>44088</v>
@@ -11558,7 +11561,7 @@
     </row>
     <row r="373" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A373" t="s">
-        <v>51</v>
+        <v>41</v>
       </c>
       <c r="B373" s="2">
         <v>44090</v>
@@ -11587,7 +11590,7 @@
     </row>
     <row r="374" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A374" t="s">
-        <v>51</v>
+        <v>41</v>
       </c>
       <c r="B374" s="2">
         <v>44092</v>
@@ -11616,7 +11619,7 @@
     </row>
     <row r="375" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A375" t="s">
-        <v>51</v>
+        <v>41</v>
       </c>
       <c r="B375" s="2">
         <v>44095</v>
@@ -11645,7 +11648,7 @@
     </row>
     <row r="376" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A376" t="s">
-        <v>51</v>
+        <v>41</v>
       </c>
       <c r="B376" s="2">
         <v>44097</v>
@@ -11674,7 +11677,7 @@
     </row>
     <row r="377" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A377" t="s">
-        <v>51</v>
+        <v>41</v>
       </c>
       <c r="B377" s="2">
         <v>44099</v>
@@ -11703,7 +11706,7 @@
     </row>
     <row r="378" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A378" t="s">
-        <v>51</v>
+        <v>41</v>
       </c>
       <c r="B378" s="2">
         <v>44102</v>
@@ -11732,7 +11735,7 @@
     </row>
     <row r="379" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A379" t="s">
-        <v>51</v>
+        <v>41</v>
       </c>
       <c r="B379" s="2">
         <v>44104</v>
@@ -11761,7 +11764,7 @@
     </row>
     <row r="380" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A380" t="s">
-        <v>51</v>
+        <v>41</v>
       </c>
       <c r="B380" s="2">
         <v>44106</v>
@@ -11790,7 +11793,7 @@
     </row>
     <row r="381" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A381" t="s">
-        <v>51</v>
+        <v>41</v>
       </c>
       <c r="B381" s="2">
         <v>44109</v>
@@ -11819,7 +11822,7 @@
     </row>
     <row r="382" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A382" t="s">
-        <v>51</v>
+        <v>41</v>
       </c>
       <c r="B382" s="2">
         <v>44111</v>
@@ -11848,7 +11851,7 @@
     </row>
     <row r="383" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A383" t="s">
-        <v>51</v>
+        <v>41</v>
       </c>
       <c r="B383" s="2">
         <v>44113</v>
@@ -11877,7 +11880,7 @@
     </row>
     <row r="384" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A384" t="s">
-        <v>51</v>
+        <v>41</v>
       </c>
       <c r="B384" s="2">
         <v>44116</v>
@@ -11906,7 +11909,7 @@
     </row>
     <row r="385" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A385" t="s">
-        <v>51</v>
+        <v>41</v>
       </c>
       <c r="B385" s="2">
         <v>44118</v>
@@ -11935,7 +11938,7 @@
     </row>
     <row r="386" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A386" t="s">
-        <v>51</v>
+        <v>41</v>
       </c>
       <c r="B386" s="2">
         <v>44120</v>
@@ -11964,7 +11967,7 @@
     </row>
     <row r="387" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A387" t="s">
-        <v>51</v>
+        <v>41</v>
       </c>
       <c r="B387" s="2">
         <v>44123</v>
@@ -11993,7 +11996,7 @@
     </row>
     <row r="388" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A388" t="s">
-        <v>51</v>
+        <v>41</v>
       </c>
       <c r="B388" s="2">
         <v>44125</v>
@@ -12022,7 +12025,7 @@
     </row>
     <row r="389" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A389" t="s">
-        <v>51</v>
+        <v>41</v>
       </c>
       <c r="B389" s="2">
         <v>44127</v>
@@ -12051,7 +12054,7 @@
     </row>
     <row r="390" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A390" t="s">
-        <v>51</v>
+        <v>41</v>
       </c>
       <c r="B390" s="2">
         <v>44131</v>
@@ -12086,7 +12089,7 @@
     </row>
     <row r="391" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A391" t="s">
-        <v>52</v>
+        <v>42</v>
       </c>
       <c r="B391" s="2">
         <v>44442</v>
@@ -12115,7 +12118,7 @@
     </row>
     <row r="392" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A392" t="s">
-        <v>52</v>
+        <v>42</v>
       </c>
       <c r="B392" s="2">
         <v>44448</v>
@@ -12144,7 +12147,7 @@
     </row>
     <row r="393" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A393" t="s">
-        <v>52</v>
+        <v>42</v>
       </c>
       <c r="B393" s="2">
         <v>44452</v>
@@ -12173,7 +12176,7 @@
     </row>
     <row r="394" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A394" t="s">
-        <v>52</v>
+        <v>42</v>
       </c>
       <c r="B394" s="2">
         <v>44456</v>
@@ -12202,7 +12205,7 @@
     </row>
     <row r="395" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A395" t="s">
-        <v>52</v>
+        <v>42</v>
       </c>
       <c r="B395" s="2">
         <v>44460</v>
@@ -12231,7 +12234,7 @@
     </row>
     <row r="396" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A396" t="s">
-        <v>52</v>
+        <v>42</v>
       </c>
       <c r="B396" s="2">
         <v>44463</v>
@@ -12260,7 +12263,7 @@
     </row>
     <row r="397" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A397" t="s">
-        <v>52</v>
+        <v>42</v>
       </c>
       <c r="B397" s="2">
         <v>44467</v>
@@ -12289,7 +12292,7 @@
     </row>
     <row r="398" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A398" t="s">
-        <v>52</v>
+        <v>42</v>
       </c>
       <c r="B398" s="2">
         <v>44470</v>
@@ -12318,7 +12321,7 @@
     </row>
     <row r="399" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A399" t="s">
-        <v>52</v>
+        <v>42</v>
       </c>
       <c r="B399" s="2">
         <v>44474</v>
@@ -12347,7 +12350,7 @@
     </row>
     <row r="400" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A400" t="s">
-        <v>52</v>
+        <v>42</v>
       </c>
       <c r="B400" s="2">
         <v>44477</v>
@@ -12376,7 +12379,7 @@
     </row>
     <row r="401" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A401" t="s">
-        <v>52</v>
+        <v>42</v>
       </c>
       <c r="B401" s="2">
         <v>44481</v>
@@ -12405,7 +12408,7 @@
     </row>
     <row r="402" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A402" t="s">
-        <v>52</v>
+        <v>42</v>
       </c>
       <c r="B402" s="2">
         <v>44484</v>
@@ -12434,7 +12437,7 @@
     </row>
     <row r="403" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A403" t="s">
-        <v>52</v>
+        <v>42</v>
       </c>
       <c r="B403" s="2">
         <v>44490</v>
@@ -12463,7 +12466,7 @@
     </row>
     <row r="404" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A404" t="s">
-        <v>52</v>
+        <v>42</v>
       </c>
       <c r="B404" s="2">
         <v>44495</v>
@@ -12492,7 +12495,7 @@
     </row>
     <row r="405" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A405" t="s">
-        <v>52</v>
+        <v>42</v>
       </c>
       <c r="B405" s="2">
         <v>44501</v>
@@ -12527,7 +12530,7 @@
     </row>
     <row r="406" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A406" t="s">
-        <v>53</v>
+        <v>43</v>
       </c>
       <c r="B406" s="2">
         <v>44442</v>
@@ -12556,7 +12559,7 @@
     </row>
     <row r="407" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A407" t="s">
-        <v>53</v>
+        <v>43</v>
       </c>
       <c r="B407" s="2">
         <v>44448</v>
@@ -12585,7 +12588,7 @@
     </row>
     <row r="408" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A408" t="s">
-        <v>53</v>
+        <v>43</v>
       </c>
       <c r="B408" s="2">
         <v>44452</v>
@@ -12614,7 +12617,7 @@
     </row>
     <row r="409" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A409" t="s">
-        <v>53</v>
+        <v>43</v>
       </c>
       <c r="B409" s="2">
         <v>44456</v>
@@ -12643,7 +12646,7 @@
     </row>
     <row r="410" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A410" t="s">
-        <v>53</v>
+        <v>43</v>
       </c>
       <c r="B410" s="2">
         <v>44460</v>
@@ -12672,7 +12675,7 @@
     </row>
     <row r="411" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A411" t="s">
-        <v>53</v>
+        <v>43</v>
       </c>
       <c r="B411" s="2">
         <v>44463</v>
@@ -12701,7 +12704,7 @@
     </row>
     <row r="412" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A412" t="s">
-        <v>53</v>
+        <v>43</v>
       </c>
       <c r="B412" s="2">
         <v>44467</v>
@@ -12730,7 +12733,7 @@
     </row>
     <row r="413" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A413" t="s">
-        <v>53</v>
+        <v>43</v>
       </c>
       <c r="B413" s="2">
         <v>44470</v>
@@ -12759,7 +12762,7 @@
     </row>
     <row r="414" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A414" t="s">
-        <v>53</v>
+        <v>43</v>
       </c>
       <c r="B414" s="2">
         <v>44474</v>
@@ -12788,7 +12791,7 @@
     </row>
     <row r="415" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A415" t="s">
-        <v>53</v>
+        <v>43</v>
       </c>
       <c r="B415" s="2">
         <v>44477</v>
@@ -12817,7 +12820,7 @@
     </row>
     <row r="416" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A416" t="s">
-        <v>53</v>
+        <v>43</v>
       </c>
       <c r="B416" s="2">
         <v>44481</v>
@@ -12846,7 +12849,7 @@
     </row>
     <row r="417" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A417" t="s">
-        <v>53</v>
+        <v>43</v>
       </c>
       <c r="B417" s="2">
         <v>44484</v>
@@ -12875,7 +12878,7 @@
     </row>
     <row r="418" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A418" t="s">
-        <v>53</v>
+        <v>43</v>
       </c>
       <c r="B418" s="2">
         <v>44490</v>
@@ -12904,7 +12907,7 @@
     </row>
     <row r="419" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A419" t="s">
-        <v>53</v>
+        <v>43</v>
       </c>
       <c r="B419" s="2">
         <v>44495</v>
@@ -12933,7 +12936,7 @@
     </row>
     <row r="420" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A420" t="s">
-        <v>53</v>
+        <v>43</v>
       </c>
       <c r="B420" s="2">
         <v>44501</v>
@@ -12968,7 +12971,7 @@
     </row>
     <row r="421" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A421" t="s">
-        <v>54</v>
+        <v>44</v>
       </c>
       <c r="B421" s="2">
         <v>44442</v>
@@ -12997,7 +13000,7 @@
     </row>
     <row r="422" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A422" t="s">
-        <v>54</v>
+        <v>44</v>
       </c>
       <c r="B422" s="2">
         <v>44448</v>
@@ -13026,7 +13029,7 @@
     </row>
     <row r="423" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A423" t="s">
-        <v>54</v>
+        <v>44</v>
       </c>
       <c r="B423" s="2">
         <v>44452</v>
@@ -13055,7 +13058,7 @@
     </row>
     <row r="424" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A424" t="s">
-        <v>54</v>
+        <v>44</v>
       </c>
       <c r="B424" s="2">
         <v>44456</v>
@@ -13084,7 +13087,7 @@
     </row>
     <row r="425" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A425" t="s">
-        <v>54</v>
+        <v>44</v>
       </c>
       <c r="B425" s="2">
         <v>44460</v>
@@ -13113,7 +13116,7 @@
     </row>
     <row r="426" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A426" t="s">
-        <v>54</v>
+        <v>44</v>
       </c>
       <c r="B426" s="2">
         <v>44463</v>
@@ -13142,7 +13145,7 @@
     </row>
     <row r="427" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A427" t="s">
-        <v>54</v>
+        <v>44</v>
       </c>
       <c r="B427" s="2">
         <v>44467</v>
@@ -13171,7 +13174,7 @@
     </row>
     <row r="428" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A428" t="s">
-        <v>54</v>
+        <v>44</v>
       </c>
       <c r="B428" s="2">
         <v>44470</v>
@@ -13200,7 +13203,7 @@
     </row>
     <row r="429" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A429" t="s">
-        <v>54</v>
+        <v>44</v>
       </c>
       <c r="B429" s="2">
         <v>44474</v>
@@ -13229,7 +13232,7 @@
     </row>
     <row r="430" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A430" t="s">
-        <v>54</v>
+        <v>44</v>
       </c>
       <c r="B430" s="2">
         <v>44477</v>
@@ -13258,7 +13261,7 @@
     </row>
     <row r="431" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A431" t="s">
-        <v>54</v>
+        <v>44</v>
       </c>
       <c r="B431" s="2">
         <v>44481</v>
@@ -13287,7 +13290,7 @@
     </row>
     <row r="432" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A432" t="s">
-        <v>54</v>
+        <v>44</v>
       </c>
       <c r="B432" s="2">
         <v>44484</v>
@@ -13316,7 +13319,7 @@
     </row>
     <row r="433" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A433" t="s">
-        <v>54</v>
+        <v>44</v>
       </c>
       <c r="B433" s="2">
         <v>44490</v>
@@ -13345,7 +13348,7 @@
     </row>
     <row r="434" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A434" t="s">
-        <v>54</v>
+        <v>44</v>
       </c>
       <c r="B434" s="2">
         <v>44495</v>
@@ -13374,7 +13377,7 @@
     </row>
     <row r="435" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A435" t="s">
-        <v>54</v>
+        <v>44</v>
       </c>
       <c r="B435" s="2">
         <v>44501</v>
@@ -13409,7 +13412,7 @@
     </row>
     <row r="436" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A436" t="s">
-        <v>55</v>
+        <v>45</v>
       </c>
       <c r="B436" s="2">
         <v>44442</v>
@@ -13438,7 +13441,7 @@
     </row>
     <row r="437" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A437" t="s">
-        <v>55</v>
+        <v>45</v>
       </c>
       <c r="B437" s="2">
         <v>44448</v>
@@ -13467,7 +13470,7 @@
     </row>
     <row r="438" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A438" t="s">
-        <v>55</v>
+        <v>45</v>
       </c>
       <c r="B438" s="2">
         <v>44452</v>
@@ -13496,7 +13499,7 @@
     </row>
     <row r="439" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A439" t="s">
-        <v>55</v>
+        <v>45</v>
       </c>
       <c r="B439" s="2">
         <v>44456</v>
@@ -13525,7 +13528,7 @@
     </row>
     <row r="440" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A440" t="s">
-        <v>55</v>
+        <v>45</v>
       </c>
       <c r="B440" s="2">
         <v>44460</v>
@@ -13554,7 +13557,7 @@
     </row>
     <row r="441" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A441" t="s">
-        <v>55</v>
+        <v>45</v>
       </c>
       <c r="B441" s="2">
         <v>44463</v>
@@ -13583,7 +13586,7 @@
     </row>
     <row r="442" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A442" t="s">
-        <v>55</v>
+        <v>45</v>
       </c>
       <c r="B442" s="2">
         <v>44467</v>
@@ -13612,7 +13615,7 @@
     </row>
     <row r="443" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A443" t="s">
-        <v>55</v>
+        <v>45</v>
       </c>
       <c r="B443" s="2">
         <v>44470</v>
@@ -13641,7 +13644,7 @@
     </row>
     <row r="444" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A444" t="s">
-        <v>55</v>
+        <v>45</v>
       </c>
       <c r="B444" s="2">
         <v>44474</v>
@@ -13670,7 +13673,7 @@
     </row>
     <row r="445" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A445" t="s">
-        <v>55</v>
+        <v>45</v>
       </c>
       <c r="B445" s="2">
         <v>44477</v>
@@ -13699,7 +13702,7 @@
     </row>
     <row r="446" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A446" t="s">
-        <v>55</v>
+        <v>45</v>
       </c>
       <c r="B446" s="2">
         <v>44481</v>
@@ -13728,7 +13731,7 @@
     </row>
     <row r="447" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A447" t="s">
-        <v>55</v>
+        <v>45</v>
       </c>
       <c r="B447" s="2">
         <v>44484</v>
@@ -13757,7 +13760,7 @@
     </row>
     <row r="448" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A448" t="s">
-        <v>55</v>
+        <v>45</v>
       </c>
       <c r="B448" s="2">
         <v>44490</v>
@@ -13786,7 +13789,7 @@
     </row>
     <row r="449" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A449" t="s">
-        <v>55</v>
+        <v>45</v>
       </c>
       <c r="B449" s="2">
         <v>44495</v>
@@ -13815,7 +13818,7 @@
     </row>
     <row r="450" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A450" t="s">
-        <v>55</v>
+        <v>45</v>
       </c>
       <c r="B450" s="2">
         <v>44501</v>
@@ -13850,7 +13853,7 @@
     </row>
     <row r="451" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A451" t="s">
-        <v>56</v>
+        <v>46</v>
       </c>
       <c r="B451" s="2">
         <v>44442</v>
@@ -13879,7 +13882,7 @@
     </row>
     <row r="452" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A452" t="s">
-        <v>56</v>
+        <v>46</v>
       </c>
       <c r="B452" s="2">
         <v>44448</v>
@@ -13908,7 +13911,7 @@
     </row>
     <row r="453" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A453" t="s">
-        <v>56</v>
+        <v>46</v>
       </c>
       <c r="B453" s="2">
         <v>44452</v>
@@ -13937,7 +13940,7 @@
     </row>
     <row r="454" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A454" t="s">
-        <v>56</v>
+        <v>46</v>
       </c>
       <c r="B454" s="2">
         <v>44456</v>
@@ -13966,7 +13969,7 @@
     </row>
     <row r="455" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A455" t="s">
-        <v>56</v>
+        <v>46</v>
       </c>
       <c r="B455" s="2">
         <v>44460</v>
@@ -13995,7 +13998,7 @@
     </row>
     <row r="456" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A456" t="s">
-        <v>56</v>
+        <v>46</v>
       </c>
       <c r="B456" s="2">
         <v>44463</v>
@@ -14024,7 +14027,7 @@
     </row>
     <row r="457" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A457" t="s">
-        <v>56</v>
+        <v>46</v>
       </c>
       <c r="B457" s="2">
         <v>44467</v>
@@ -14053,7 +14056,7 @@
     </row>
     <row r="458" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A458" t="s">
-        <v>56</v>
+        <v>46</v>
       </c>
       <c r="B458" s="2">
         <v>44470</v>
@@ -14082,7 +14085,7 @@
     </row>
     <row r="459" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A459" t="s">
-        <v>56</v>
+        <v>46</v>
       </c>
       <c r="B459" s="2">
         <v>44474</v>
@@ -14111,7 +14114,7 @@
     </row>
     <row r="460" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A460" t="s">
-        <v>56</v>
+        <v>46</v>
       </c>
       <c r="B460" s="2">
         <v>44477</v>
@@ -14140,7 +14143,7 @@
     </row>
     <row r="461" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A461" t="s">
-        <v>56</v>
+        <v>46</v>
       </c>
       <c r="B461" s="2">
         <v>44481</v>
@@ -14169,7 +14172,7 @@
     </row>
     <row r="462" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A462" t="s">
-        <v>56</v>
+        <v>46</v>
       </c>
       <c r="B462" s="2">
         <v>44484</v>
@@ -14198,7 +14201,7 @@
     </row>
     <row r="463" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A463" t="s">
-        <v>56</v>
+        <v>46</v>
       </c>
       <c r="B463" s="2">
         <v>44490</v>
@@ -14227,7 +14230,7 @@
     </row>
     <row r="464" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A464" t="s">
-        <v>56</v>
+        <v>46</v>
       </c>
       <c r="B464" s="2">
         <v>44495</v>
@@ -14256,7 +14259,7 @@
     </row>
     <row r="465" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A465" t="s">
-        <v>56</v>
+        <v>46</v>
       </c>
       <c r="B465" s="2">
         <v>44501</v>
@@ -14291,7 +14294,7 @@
     </row>
     <row r="466" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A466" t="s">
-        <v>57</v>
+        <v>47</v>
       </c>
       <c r="B466" s="2">
         <v>44088</v>
@@ -14320,7 +14323,7 @@
     </row>
     <row r="467" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A467" t="s">
-        <v>57</v>
+        <v>47</v>
       </c>
       <c r="B467" s="2">
         <v>44092</v>
@@ -14349,7 +14352,7 @@
     </row>
     <row r="468" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A468" t="s">
-        <v>57</v>
+        <v>47</v>
       </c>
       <c r="B468" s="2">
         <v>44095</v>
@@ -14378,7 +14381,7 @@
     </row>
     <row r="469" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A469" t="s">
-        <v>57</v>
+        <v>47</v>
       </c>
       <c r="B469" s="2">
         <v>44098</v>
@@ -14407,7 +14410,7 @@
     </row>
     <row r="470" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A470" t="s">
-        <v>57</v>
+        <v>47</v>
       </c>
       <c r="B470" s="2">
         <v>44102</v>
@@ -14436,7 +14439,7 @@
     </row>
     <row r="471" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A471" t="s">
-        <v>57</v>
+        <v>47</v>
       </c>
       <c r="B471" s="2">
         <v>44104</v>
@@ -14465,7 +14468,7 @@
     </row>
     <row r="472" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A472" t="s">
-        <v>57</v>
+        <v>47</v>
       </c>
       <c r="B472" s="2">
         <v>44106</v>
@@ -14494,7 +14497,7 @@
     </row>
     <row r="473" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A473" t="s">
-        <v>57</v>
+        <v>47</v>
       </c>
       <c r="B473" s="2">
         <v>44109</v>
@@ -14523,7 +14526,7 @@
     </row>
     <row r="474" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A474" t="s">
-        <v>57</v>
+        <v>47</v>
       </c>
       <c r="B474" s="2">
         <v>44022</v>
@@ -14552,7 +14555,7 @@
     </row>
     <row r="475" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A475" t="s">
-        <v>57</v>
+        <v>47</v>
       </c>
       <c r="B475" s="2">
         <v>44175</v>
@@ -14581,7 +14584,7 @@
     </row>
     <row r="476" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A476" t="s">
-        <v>57</v>
+        <v>47</v>
       </c>
       <c r="B476" s="2">
         <v>44118</v>
@@ -14610,7 +14613,7 @@
     </row>
     <row r="477" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A477" t="s">
-        <v>57</v>
+        <v>47</v>
       </c>
       <c r="B477" s="2">
         <v>44120</v>
@@ -14639,7 +14642,7 @@
     </row>
     <row r="478" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A478" t="s">
-        <v>57</v>
+        <v>47</v>
       </c>
       <c r="B478" s="2">
         <v>44123</v>
@@ -14668,7 +14671,7 @@
     </row>
     <row r="479" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A479" t="s">
-        <v>57</v>
+        <v>47</v>
       </c>
       <c r="B479" s="2">
         <v>44127</v>
@@ -14703,7 +14706,7 @@
     </row>
     <row r="480" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A480" t="s">
-        <v>58</v>
+        <v>48</v>
       </c>
       <c r="B480" s="2">
         <v>44088</v>
@@ -14732,7 +14735,7 @@
     </row>
     <row r="481" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A481" t="s">
-        <v>58</v>
+        <v>48</v>
       </c>
       <c r="B481" s="2">
         <v>44092</v>
@@ -14761,7 +14764,7 @@
     </row>
     <row r="482" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A482" t="s">
-        <v>58</v>
+        <v>48</v>
       </c>
       <c r="B482" s="2">
         <v>44095</v>
@@ -14790,7 +14793,7 @@
     </row>
     <row r="483" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A483" t="s">
-        <v>58</v>
+        <v>48</v>
       </c>
       <c r="B483" s="2">
         <v>44098</v>
@@ -14819,7 +14822,7 @@
     </row>
     <row r="484" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A484" t="s">
-        <v>58</v>
+        <v>48</v>
       </c>
       <c r="B484" s="2">
         <v>44102</v>
@@ -14848,7 +14851,7 @@
     </row>
     <row r="485" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A485" t="s">
-        <v>58</v>
+        <v>48</v>
       </c>
       <c r="B485" s="2">
         <v>44104</v>
@@ -14877,7 +14880,7 @@
     </row>
     <row r="486" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A486" t="s">
-        <v>58</v>
+        <v>48</v>
       </c>
       <c r="B486" s="2">
         <v>44106</v>
@@ -14906,7 +14909,7 @@
     </row>
     <row r="487" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A487" t="s">
-        <v>58</v>
+        <v>48</v>
       </c>
       <c r="B487" s="2">
         <v>44109</v>
@@ -14935,7 +14938,7 @@
     </row>
     <row r="488" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A488" t="s">
-        <v>58</v>
+        <v>48</v>
       </c>
       <c r="B488" s="2">
         <v>44022</v>
@@ -14964,7 +14967,7 @@
     </row>
     <row r="489" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A489" t="s">
-        <v>58</v>
+        <v>48</v>
       </c>
       <c r="B489" s="2">
         <v>44175</v>
@@ -14993,7 +14996,7 @@
     </row>
     <row r="490" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A490" t="s">
-        <v>58</v>
+        <v>48</v>
       </c>
       <c r="B490" s="2">
         <v>44118</v>
@@ -15022,7 +15025,7 @@
     </row>
     <row r="491" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A491" t="s">
-        <v>58</v>
+        <v>48</v>
       </c>
       <c r="B491" s="2">
         <v>44120</v>
@@ -15051,7 +15054,7 @@
     </row>
     <row r="492" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A492" t="s">
-        <v>58</v>
+        <v>48</v>
       </c>
       <c r="B492" s="2">
         <v>44123</v>
@@ -15080,7 +15083,7 @@
     </row>
     <row r="493" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A493" t="s">
-        <v>58</v>
+        <v>48</v>
       </c>
       <c r="B493" s="2">
         <v>44127</v>
@@ -15115,7 +15118,7 @@
     </row>
     <row r="494" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A494" t="s">
-        <v>59</v>
+        <v>49</v>
       </c>
       <c r="B494" s="2">
         <v>44088</v>
@@ -15144,7 +15147,7 @@
     </row>
     <row r="495" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A495" t="s">
-        <v>59</v>
+        <v>49</v>
       </c>
       <c r="B495" s="2">
         <v>44092</v>
@@ -15173,7 +15176,7 @@
     </row>
     <row r="496" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A496" t="s">
-        <v>59</v>
+        <v>49</v>
       </c>
       <c r="B496" s="2">
         <v>44095</v>
@@ -15202,7 +15205,7 @@
     </row>
     <row r="497" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A497" t="s">
-        <v>59</v>
+        <v>49</v>
       </c>
       <c r="B497" s="2">
         <v>44098</v>
@@ -15231,7 +15234,7 @@
     </row>
     <row r="498" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A498" t="s">
-        <v>59</v>
+        <v>49</v>
       </c>
       <c r="B498" s="2">
         <v>44102</v>
@@ -15260,7 +15263,7 @@
     </row>
     <row r="499" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A499" t="s">
-        <v>59</v>
+        <v>49</v>
       </c>
       <c r="B499" s="2">
         <v>44104</v>
@@ -15289,7 +15292,7 @@
     </row>
     <row r="500" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A500" t="s">
-        <v>59</v>
+        <v>49</v>
       </c>
       <c r="B500" s="2">
         <v>44106</v>
@@ -15318,7 +15321,7 @@
     </row>
     <row r="501" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A501" t="s">
-        <v>59</v>
+        <v>49</v>
       </c>
       <c r="B501" s="2">
         <v>44109</v>
@@ -15347,7 +15350,7 @@
     </row>
     <row r="502" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A502" t="s">
-        <v>59</v>
+        <v>49</v>
       </c>
       <c r="B502" s="2">
         <v>44022</v>
@@ -15376,7 +15379,7 @@
     </row>
     <row r="503" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A503" t="s">
-        <v>59</v>
+        <v>49</v>
       </c>
       <c r="B503" s="2">
         <v>44175</v>
@@ -15405,7 +15408,7 @@
     </row>
     <row r="504" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A504" t="s">
-        <v>59</v>
+        <v>49</v>
       </c>
       <c r="B504" s="2">
         <v>44118</v>
@@ -15434,7 +15437,7 @@
     </row>
     <row r="505" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A505" t="s">
-        <v>59</v>
+        <v>49</v>
       </c>
       <c r="B505" s="2">
         <v>44120</v>
@@ -15463,7 +15466,7 @@
     </row>
     <row r="506" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A506" t="s">
-        <v>59</v>
+        <v>49</v>
       </c>
       <c r="B506" s="2">
         <v>44123</v>
@@ -15492,7 +15495,7 @@
     </row>
     <row r="507" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A507" t="s">
-        <v>59</v>
+        <v>49</v>
       </c>
       <c r="B507" s="2">
         <v>44127</v>
@@ -15534,6 +15537,9 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:I384"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="59.33203125" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
@@ -15555,10 +15561,10 @@
         <v>5</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>61</v>
+        <v>51</v>
       </c>
       <c r="I1" s="1" t="s">
         <v>10</v>
@@ -18691,7 +18697,7 @@
     </row>
     <row r="120" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A120" t="s">
-        <v>36</v>
+        <v>52</v>
       </c>
       <c r="B120" s="2">
         <v>43402</v>
@@ -18706,7 +18712,7 @@
         <v>25</v>
       </c>
       <c r="F120" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="G120">
         <v>0</v>
@@ -18717,7 +18723,7 @@
     </row>
     <row r="121" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A121" t="s">
-        <v>36</v>
+        <v>52</v>
       </c>
       <c r="B121" s="2">
         <v>43404</v>
@@ -18732,7 +18738,7 @@
         <v>25</v>
       </c>
       <c r="F121" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="G121">
         <v>0</v>
@@ -18743,7 +18749,7 @@
     </row>
     <row r="122" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A122" t="s">
-        <v>36</v>
+        <v>52</v>
       </c>
       <c r="B122" s="2">
         <v>43406</v>
@@ -18758,7 +18764,7 @@
         <v>25</v>
       </c>
       <c r="F122" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="G122">
         <v>0</v>
@@ -18769,7 +18775,7 @@
     </row>
     <row r="123" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A123" t="s">
-        <v>36</v>
+        <v>52</v>
       </c>
       <c r="B123" s="2">
         <v>43409</v>
@@ -18784,7 +18790,7 @@
         <v>25</v>
       </c>
       <c r="F123" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="G123">
         <v>0</v>
@@ -18795,7 +18801,7 @@
     </row>
     <row r="124" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A124" t="s">
-        <v>36</v>
+        <v>52</v>
       </c>
       <c r="B124" s="2">
         <v>43411</v>
@@ -18810,7 +18816,7 @@
         <v>25</v>
       </c>
       <c r="F124" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="G124">
         <v>0</v>
@@ -18821,7 +18827,7 @@
     </row>
     <row r="125" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A125" t="s">
-        <v>36</v>
+        <v>52</v>
       </c>
       <c r="B125" s="2">
         <v>43413</v>
@@ -18836,7 +18842,7 @@
         <v>25</v>
       </c>
       <c r="F125" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="G125">
         <v>0</v>
@@ -18847,7 +18853,7 @@
     </row>
     <row r="126" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A126" t="s">
-        <v>36</v>
+        <v>52</v>
       </c>
       <c r="B126" s="2">
         <v>43416</v>
@@ -18862,7 +18868,7 @@
         <v>25</v>
       </c>
       <c r="F126" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="G126">
         <v>0</v>
@@ -18873,7 +18879,7 @@
     </row>
     <row r="127" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A127" t="s">
-        <v>36</v>
+        <v>52</v>
       </c>
       <c r="B127" s="2">
         <v>43418</v>
@@ -18888,7 +18894,7 @@
         <v>25</v>
       </c>
       <c r="F127" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="G127">
         <v>0</v>
@@ -18899,7 +18905,7 @@
     </row>
     <row r="128" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A128" t="s">
-        <v>36</v>
+        <v>52</v>
       </c>
       <c r="B128" s="2">
         <v>43420</v>
@@ -18914,7 +18920,7 @@
         <v>25</v>
       </c>
       <c r="F128" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="G128">
         <v>0</v>
@@ -18925,7 +18931,7 @@
     </row>
     <row r="129" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A129" t="s">
-        <v>36</v>
+        <v>52</v>
       </c>
       <c r="B129" s="2">
         <v>43423</v>
@@ -18940,7 +18946,7 @@
         <v>25</v>
       </c>
       <c r="F129" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="G129">
         <v>0</v>
@@ -18951,7 +18957,7 @@
     </row>
     <row r="130" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A130" t="s">
-        <v>36</v>
+        <v>52</v>
       </c>
       <c r="B130" s="2">
         <v>43425</v>
@@ -18966,7 +18972,7 @@
         <v>25</v>
       </c>
       <c r="F130" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="G130">
         <v>1</v>
@@ -18977,7 +18983,7 @@
     </row>
     <row r="131" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A131" t="s">
-        <v>36</v>
+        <v>52</v>
       </c>
       <c r="B131" s="2">
         <v>43427</v>
@@ -18992,7 +18998,7 @@
         <v>25</v>
       </c>
       <c r="F131" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="G131">
         <v>4</v>
@@ -19003,7 +19009,7 @@
     </row>
     <row r="132" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A132" t="s">
-        <v>36</v>
+        <v>52</v>
       </c>
       <c r="B132" s="2">
         <v>43430</v>
@@ -19018,7 +19024,7 @@
         <v>25</v>
       </c>
       <c r="F132" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="G132">
         <v>9</v>
@@ -19029,7 +19035,7 @@
     </row>
     <row r="133" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A133" t="s">
-        <v>36</v>
+        <v>52</v>
       </c>
       <c r="B133" s="2">
         <v>43432</v>
@@ -19044,7 +19050,7 @@
         <v>25</v>
       </c>
       <c r="F133" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="G133">
         <v>10</v>
@@ -19055,7 +19061,7 @@
     </row>
     <row r="134" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A134" t="s">
-        <v>36</v>
+        <v>52</v>
       </c>
       <c r="B134" s="2">
         <v>43434</v>
@@ -19070,7 +19076,7 @@
         <v>25</v>
       </c>
       <c r="F134" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="G134">
         <v>12</v>
@@ -19081,7 +19087,7 @@
     </row>
     <row r="135" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A135" t="s">
-        <v>36</v>
+        <v>52</v>
       </c>
       <c r="B135" s="2">
         <v>43437</v>
@@ -19096,7 +19102,7 @@
         <v>25</v>
       </c>
       <c r="F135" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="G135">
         <v>12</v>
@@ -19107,7 +19113,7 @@
     </row>
     <row r="136" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A136" t="s">
-        <v>36</v>
+        <v>52</v>
       </c>
       <c r="B136" s="2">
         <v>43439</v>
@@ -19122,7 +19128,7 @@
         <v>25</v>
       </c>
       <c r="F136" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="G136">
         <v>12</v>
@@ -19133,7 +19139,7 @@
     </row>
     <row r="137" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A137" t="s">
-        <v>36</v>
+        <v>52</v>
       </c>
       <c r="B137" s="2">
         <v>43441</v>
@@ -19148,7 +19154,7 @@
         <v>25</v>
       </c>
       <c r="F137" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="G137">
         <v>12</v>
@@ -19159,7 +19165,7 @@
     </row>
     <row r="138" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A138" t="s">
-        <v>36</v>
+        <v>52</v>
       </c>
       <c r="B138" s="2">
         <v>43444</v>
@@ -19174,7 +19180,7 @@
         <v>25</v>
       </c>
       <c r="F138" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="G138">
         <v>12</v>
@@ -19185,7 +19191,7 @@
     </row>
     <row r="139" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A139" t="s">
-        <v>36</v>
+        <v>52</v>
       </c>
       <c r="B139" s="2">
         <v>43446</v>
@@ -19200,7 +19206,7 @@
         <v>25</v>
       </c>
       <c r="F139" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="G139">
         <v>12</v>
@@ -19214,7 +19220,7 @@
     </row>
     <row r="140" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A140" t="s">
-        <v>38</v>
+        <v>53</v>
       </c>
       <c r="B140" s="2">
         <v>43402</v>
@@ -19229,7 +19235,7 @@
         <v>25</v>
       </c>
       <c r="F140" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="G140">
         <v>0</v>
@@ -19240,7 +19246,7 @@
     </row>
     <row r="141" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A141" t="s">
-        <v>38</v>
+        <v>53</v>
       </c>
       <c r="B141" s="2">
         <v>43404</v>
@@ -19255,7 +19261,7 @@
         <v>25</v>
       </c>
       <c r="F141" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="G141">
         <v>0</v>
@@ -19266,7 +19272,7 @@
     </row>
     <row r="142" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A142" t="s">
-        <v>38</v>
+        <v>53</v>
       </c>
       <c r="B142" s="2">
         <v>43406</v>
@@ -19281,7 +19287,7 @@
         <v>25</v>
       </c>
       <c r="F142" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="G142">
         <v>0</v>
@@ -19292,7 +19298,7 @@
     </row>
     <row r="143" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A143" t="s">
-        <v>38</v>
+        <v>53</v>
       </c>
       <c r="B143" s="2">
         <v>43409</v>
@@ -19307,7 +19313,7 @@
         <v>25</v>
       </c>
       <c r="F143" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="G143">
         <v>0</v>
@@ -19318,7 +19324,7 @@
     </row>
     <row r="144" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A144" t="s">
-        <v>38</v>
+        <v>53</v>
       </c>
       <c r="B144" s="2">
         <v>43411</v>
@@ -19333,7 +19339,7 @@
         <v>25</v>
       </c>
       <c r="F144" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="G144">
         <v>0</v>
@@ -19344,7 +19350,7 @@
     </row>
     <row r="145" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A145" t="s">
-        <v>38</v>
+        <v>53</v>
       </c>
       <c r="B145" s="2">
         <v>43413</v>
@@ -19359,7 +19365,7 @@
         <v>25</v>
       </c>
       <c r="F145" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="G145">
         <v>0</v>
@@ -19370,7 +19376,7 @@
     </row>
     <row r="146" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A146" t="s">
-        <v>38</v>
+        <v>53</v>
       </c>
       <c r="B146" s="2">
         <v>43416</v>
@@ -19385,7 +19391,7 @@
         <v>25</v>
       </c>
       <c r="F146" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="G146">
         <v>0</v>
@@ -19396,7 +19402,7 @@
     </row>
     <row r="147" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A147" t="s">
-        <v>38</v>
+        <v>53</v>
       </c>
       <c r="B147" s="2">
         <v>43418</v>
@@ -19411,7 +19417,7 @@
         <v>25</v>
       </c>
       <c r="F147" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="G147">
         <v>0</v>
@@ -19422,7 +19428,7 @@
     </row>
     <row r="148" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A148" t="s">
-        <v>38</v>
+        <v>53</v>
       </c>
       <c r="B148" s="2">
         <v>43420</v>
@@ -19437,7 +19443,7 @@
         <v>25</v>
       </c>
       <c r="F148" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="G148">
         <v>0</v>
@@ -19448,7 +19454,7 @@
     </row>
     <row r="149" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A149" t="s">
-        <v>38</v>
+        <v>53</v>
       </c>
       <c r="B149" s="2">
         <v>43423</v>
@@ -19463,7 +19469,7 @@
         <v>25</v>
       </c>
       <c r="F149" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="G149">
         <v>0</v>
@@ -19474,7 +19480,7 @@
     </row>
     <row r="150" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A150" t="s">
-        <v>38</v>
+        <v>53</v>
       </c>
       <c r="B150" s="2">
         <v>43425</v>
@@ -19489,7 +19495,7 @@
         <v>25</v>
       </c>
       <c r="F150" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="G150">
         <v>1</v>
@@ -19500,7 +19506,7 @@
     </row>
     <row r="151" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A151" t="s">
-        <v>38</v>
+        <v>53</v>
       </c>
       <c r="B151" s="2">
         <v>43427</v>
@@ -19515,7 +19521,7 @@
         <v>25</v>
       </c>
       <c r="F151" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="G151">
         <v>4</v>
@@ -19526,7 +19532,7 @@
     </row>
     <row r="152" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A152" t="s">
-        <v>38</v>
+        <v>53</v>
       </c>
       <c r="B152" s="2">
         <v>43430</v>
@@ -19541,7 +19547,7 @@
         <v>25</v>
       </c>
       <c r="F152" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="G152">
         <v>9</v>
@@ -19552,7 +19558,7 @@
     </row>
     <row r="153" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A153" t="s">
-        <v>38</v>
+        <v>53</v>
       </c>
       <c r="B153" s="2">
         <v>43432</v>
@@ -19567,7 +19573,7 @@
         <v>25</v>
       </c>
       <c r="F153" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="G153">
         <v>10</v>
@@ -19578,7 +19584,7 @@
     </row>
     <row r="154" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A154" t="s">
-        <v>38</v>
+        <v>53</v>
       </c>
       <c r="B154" s="2">
         <v>43434</v>
@@ -19593,7 +19599,7 @@
         <v>25</v>
       </c>
       <c r="F154" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="G154">
         <v>12</v>
@@ -19604,7 +19610,7 @@
     </row>
     <row r="155" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A155" t="s">
-        <v>38</v>
+        <v>53</v>
       </c>
       <c r="B155" s="2">
         <v>43437</v>
@@ -19619,7 +19625,7 @@
         <v>25</v>
       </c>
       <c r="F155" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="G155">
         <v>12</v>
@@ -19630,7 +19636,7 @@
     </row>
     <row r="156" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A156" t="s">
-        <v>38</v>
+        <v>53</v>
       </c>
       <c r="B156" s="2">
         <v>43439</v>
@@ -19645,7 +19651,7 @@
         <v>25</v>
       </c>
       <c r="F156" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="G156">
         <v>12</v>
@@ -19656,7 +19662,7 @@
     </row>
     <row r="157" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A157" t="s">
-        <v>38</v>
+        <v>53</v>
       </c>
       <c r="B157" s="2">
         <v>43441</v>
@@ -19671,7 +19677,7 @@
         <v>25</v>
       </c>
       <c r="F157" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="G157">
         <v>12</v>
@@ -19682,7 +19688,7 @@
     </row>
     <row r="158" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A158" t="s">
-        <v>38</v>
+        <v>53</v>
       </c>
       <c r="B158" s="2">
         <v>43444</v>
@@ -19697,7 +19703,7 @@
         <v>25</v>
       </c>
       <c r="F158" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="G158">
         <v>12</v>
@@ -19708,7 +19714,7 @@
     </row>
     <row r="159" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A159" t="s">
-        <v>38</v>
+        <v>53</v>
       </c>
       <c r="B159" s="2">
         <v>43446</v>
@@ -19723,7 +19729,7 @@
         <v>25</v>
       </c>
       <c r="F159" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="G159">
         <v>12</v>
@@ -19737,7 +19743,7 @@
     </row>
     <row r="160" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A160" t="s">
-        <v>39</v>
+        <v>54</v>
       </c>
       <c r="B160" s="2">
         <v>43780</v>
@@ -19752,7 +19758,7 @@
         <v>25</v>
       </c>
       <c r="F160" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="G160">
         <v>0</v>
@@ -19763,7 +19769,7 @@
     </row>
     <row r="161" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A161" t="s">
-        <v>39</v>
+        <v>54</v>
       </c>
       <c r="B161" s="2">
         <v>43782</v>
@@ -19778,7 +19784,7 @@
         <v>25</v>
       </c>
       <c r="F161" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="G161">
         <v>0</v>
@@ -19789,7 +19795,7 @@
     </row>
     <row r="162" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A162" t="s">
-        <v>39</v>
+        <v>54</v>
       </c>
       <c r="B162" s="2">
         <v>43784</v>
@@ -19804,7 +19810,7 @@
         <v>25</v>
       </c>
       <c r="F162" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="G162">
         <v>0</v>
@@ -19815,7 +19821,7 @@
     </row>
     <row r="163" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A163" t="s">
-        <v>39</v>
+        <v>54</v>
       </c>
       <c r="B163" s="2">
         <v>43787</v>
@@ -19830,7 +19836,7 @@
         <v>25</v>
       </c>
       <c r="F163" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="G163">
         <v>5</v>
@@ -19841,7 +19847,7 @@
     </row>
     <row r="164" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A164" t="s">
-        <v>39</v>
+        <v>54</v>
       </c>
       <c r="B164" s="2">
         <v>43789</v>
@@ -19856,7 +19862,7 @@
         <v>25</v>
       </c>
       <c r="F164" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="G164">
         <v>13</v>
@@ -19867,7 +19873,7 @@
     </row>
     <row r="165" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A165" t="s">
-        <v>39</v>
+        <v>54</v>
       </c>
       <c r="B165" s="2">
         <v>43791</v>
@@ -19882,7 +19888,7 @@
         <v>25</v>
       </c>
       <c r="F165" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="G165">
         <v>16</v>
@@ -19893,7 +19899,7 @@
     </row>
     <row r="166" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A166" t="s">
-        <v>39</v>
+        <v>54</v>
       </c>
       <c r="B166" s="2">
         <v>43794</v>
@@ -19908,7 +19914,7 @@
         <v>25</v>
       </c>
       <c r="F166" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="G166">
         <v>20</v>
@@ -19919,7 +19925,7 @@
     </row>
     <row r="167" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A167" t="s">
-        <v>39</v>
+        <v>54</v>
       </c>
       <c r="B167" s="2">
         <v>43796</v>
@@ -19934,7 +19940,7 @@
         <v>25</v>
       </c>
       <c r="F167" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="G167">
         <v>21</v>
@@ -19945,7 +19951,7 @@
     </row>
     <row r="168" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A168" t="s">
-        <v>39</v>
+        <v>54</v>
       </c>
       <c r="B168" s="2">
         <v>43798</v>
@@ -19960,7 +19966,7 @@
         <v>25</v>
       </c>
       <c r="F168" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="G168">
         <v>21</v>
@@ -19971,7 +19977,7 @@
     </row>
     <row r="169" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A169" t="s">
-        <v>39</v>
+        <v>54</v>
       </c>
       <c r="B169" s="2">
         <v>43801</v>
@@ -19986,7 +19992,7 @@
         <v>25</v>
       </c>
       <c r="F169" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="G169">
         <v>21</v>
@@ -19997,7 +20003,7 @@
     </row>
     <row r="170" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A170" t="s">
-        <v>39</v>
+        <v>54</v>
       </c>
       <c r="B170" s="2">
         <v>43805</v>
@@ -20012,7 +20018,7 @@
         <v>25</v>
       </c>
       <c r="F170" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="G170">
         <v>21</v>
@@ -20023,7 +20029,7 @@
     </row>
     <row r="171" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A171" t="s">
-        <v>39</v>
+        <v>54</v>
       </c>
       <c r="B171" s="2">
         <v>43808</v>
@@ -20038,7 +20044,7 @@
         <v>25</v>
       </c>
       <c r="F171" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="G171">
         <v>21</v>
@@ -20052,7 +20058,7 @@
     </row>
     <row r="172" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A172" t="s">
-        <v>41</v>
+        <v>55</v>
       </c>
       <c r="B172" s="2">
         <v>43780</v>
@@ -20067,7 +20073,7 @@
         <v>25</v>
       </c>
       <c r="F172" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="G172">
         <v>0</v>
@@ -20078,7 +20084,7 @@
     </row>
     <row r="173" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A173" t="s">
-        <v>41</v>
+        <v>55</v>
       </c>
       <c r="B173" s="2">
         <v>43782</v>
@@ -20093,7 +20099,7 @@
         <v>25</v>
       </c>
       <c r="F173" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="G173">
         <v>0</v>
@@ -20104,7 +20110,7 @@
     </row>
     <row r="174" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A174" t="s">
-        <v>41</v>
+        <v>55</v>
       </c>
       <c r="B174" s="2">
         <v>43784</v>
@@ -20119,7 +20125,7 @@
         <v>25</v>
       </c>
       <c r="F174" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="G174">
         <v>0</v>
@@ -20130,7 +20136,7 @@
     </row>
     <row r="175" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A175" t="s">
-        <v>41</v>
+        <v>55</v>
       </c>
       <c r="B175" s="2">
         <v>43787</v>
@@ -20145,7 +20151,7 @@
         <v>25</v>
       </c>
       <c r="F175" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="G175">
         <v>5</v>
@@ -20156,7 +20162,7 @@
     </row>
     <row r="176" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A176" t="s">
-        <v>41</v>
+        <v>55</v>
       </c>
       <c r="B176" s="2">
         <v>43789</v>
@@ -20171,7 +20177,7 @@
         <v>25</v>
       </c>
       <c r="F176" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="G176">
         <v>13</v>
@@ -20182,7 +20188,7 @@
     </row>
     <row r="177" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A177" t="s">
-        <v>41</v>
+        <v>55</v>
       </c>
       <c r="B177" s="2">
         <v>43791</v>
@@ -20197,7 +20203,7 @@
         <v>25</v>
       </c>
       <c r="F177" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="G177">
         <v>16</v>
@@ -20208,7 +20214,7 @@
     </row>
     <row r="178" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A178" t="s">
-        <v>41</v>
+        <v>55</v>
       </c>
       <c r="B178" s="2">
         <v>43794</v>
@@ -20223,7 +20229,7 @@
         <v>25</v>
       </c>
       <c r="F178" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="G178">
         <v>20</v>
@@ -20234,7 +20240,7 @@
     </row>
     <row r="179" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A179" t="s">
-        <v>41</v>
+        <v>55</v>
       </c>
       <c r="B179" s="2">
         <v>43796</v>
@@ -20249,7 +20255,7 @@
         <v>25</v>
       </c>
       <c r="F179" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="G179">
         <v>21</v>
@@ -20260,7 +20266,7 @@
     </row>
     <row r="180" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A180" t="s">
-        <v>41</v>
+        <v>55</v>
       </c>
       <c r="B180" s="2">
         <v>43798</v>
@@ -20275,7 +20281,7 @@
         <v>25</v>
       </c>
       <c r="F180" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="G180">
         <v>21</v>
@@ -20286,7 +20292,7 @@
     </row>
     <row r="181" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A181" t="s">
-        <v>41</v>
+        <v>55</v>
       </c>
       <c r="B181" s="2">
         <v>43801</v>
@@ -20301,7 +20307,7 @@
         <v>25</v>
       </c>
       <c r="F181" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="G181">
         <v>21</v>
@@ -20312,7 +20318,7 @@
     </row>
     <row r="182" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A182" t="s">
-        <v>41</v>
+        <v>55</v>
       </c>
       <c r="B182" s="2">
         <v>43805</v>
@@ -20327,7 +20333,7 @@
         <v>25</v>
       </c>
       <c r="F182" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="G182">
         <v>21</v>
@@ -20338,7 +20344,7 @@
     </row>
     <row r="183" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A183" t="s">
-        <v>41</v>
+        <v>55</v>
       </c>
       <c r="B183" s="2">
         <v>43808</v>
@@ -20353,7 +20359,7 @@
         <v>25</v>
       </c>
       <c r="F183" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="G183">
         <v>21</v>
@@ -20367,7 +20373,7 @@
     </row>
     <row r="184" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A184" t="s">
-        <v>42</v>
+        <v>56</v>
       </c>
       <c r="B184" s="2">
         <v>44138</v>
@@ -20382,7 +20388,7 @@
         <v>25</v>
       </c>
       <c r="F184" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="G184">
         <v>0</v>
@@ -20393,7 +20399,7 @@
     </row>
     <row r="185" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A185" t="s">
-        <v>42</v>
+        <v>56</v>
       </c>
       <c r="B185" s="2">
         <v>44141</v>
@@ -20408,7 +20414,7 @@
         <v>25</v>
       </c>
       <c r="F185" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="G185">
         <v>0</v>
@@ -20419,7 +20425,7 @@
     </row>
     <row r="186" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A186" t="s">
-        <v>42</v>
+        <v>56</v>
       </c>
       <c r="B186" s="2">
         <v>44144</v>
@@ -20434,7 +20440,7 @@
         <v>25</v>
       </c>
       <c r="F186" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="G186">
         <v>0</v>
@@ -20445,7 +20451,7 @@
     </row>
     <row r="187" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A187" t="s">
-        <v>42</v>
+        <v>56</v>
       </c>
       <c r="B187" s="2">
         <v>44146</v>
@@ -20460,7 +20466,7 @@
         <v>25</v>
       </c>
       <c r="F187" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="G187">
         <v>0</v>
@@ -20471,7 +20477,7 @@
     </row>
     <row r="188" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A188" t="s">
-        <v>42</v>
+        <v>56</v>
       </c>
       <c r="B188" s="2">
         <v>44148</v>
@@ -20486,7 +20492,7 @@
         <v>25</v>
       </c>
       <c r="F188" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="G188">
         <v>2</v>
@@ -20497,7 +20503,7 @@
     </row>
     <row r="189" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A189" t="s">
-        <v>42</v>
+        <v>56</v>
       </c>
       <c r="B189" s="2">
         <v>44151</v>
@@ -20512,7 +20518,7 @@
         <v>25</v>
       </c>
       <c r="F189" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="G189">
         <v>7</v>
@@ -20523,7 +20529,7 @@
     </row>
     <row r="190" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A190" t="s">
-        <v>42</v>
+        <v>56</v>
       </c>
       <c r="B190" s="2">
         <v>44153</v>
@@ -20538,7 +20544,7 @@
         <v>25</v>
       </c>
       <c r="F190" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="G190">
         <v>10.5</v>
@@ -20549,7 +20555,7 @@
     </row>
     <row r="191" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A191" t="s">
-        <v>42</v>
+        <v>56</v>
       </c>
       <c r="B191" s="2">
         <v>44155</v>
@@ -20564,7 +20570,7 @@
         <v>25</v>
       </c>
       <c r="F191" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="G191">
         <v>12</v>
@@ -20575,7 +20581,7 @@
     </row>
     <row r="192" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A192" t="s">
-        <v>42</v>
+        <v>56</v>
       </c>
       <c r="B192" s="2">
         <v>44158</v>
@@ -20590,7 +20596,7 @@
         <v>25</v>
       </c>
       <c r="F192" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="G192">
         <v>12.5</v>
@@ -20601,7 +20607,7 @@
     </row>
     <row r="193" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A193" t="s">
-        <v>42</v>
+        <v>56</v>
       </c>
       <c r="B193" s="2">
         <v>44160</v>
@@ -20616,7 +20622,7 @@
         <v>25</v>
       </c>
       <c r="F193" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="G193">
         <v>12.5</v>
@@ -20627,7 +20633,7 @@
     </row>
     <row r="194" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A194" t="s">
-        <v>42</v>
+        <v>56</v>
       </c>
       <c r="B194" s="2">
         <v>44162</v>
@@ -20642,7 +20648,7 @@
         <v>25</v>
       </c>
       <c r="F194" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="G194">
         <v>12.5</v>
@@ -20653,7 +20659,7 @@
     </row>
     <row r="195" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A195" t="s">
-        <v>42</v>
+        <v>56</v>
       </c>
       <c r="B195" s="2">
         <v>44165</v>
@@ -20668,7 +20674,7 @@
         <v>25</v>
       </c>
       <c r="F195" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="G195">
         <v>12.5</v>
@@ -20679,7 +20685,7 @@
     </row>
     <row r="196" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A196" t="s">
-        <v>42</v>
+        <v>56</v>
       </c>
       <c r="B196" s="2">
         <v>44167</v>
@@ -20694,7 +20700,7 @@
         <v>25</v>
       </c>
       <c r="F196" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="G196">
         <v>12.5</v>
@@ -20705,7 +20711,7 @@
     </row>
     <row r="197" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A197" t="s">
-        <v>42</v>
+        <v>56</v>
       </c>
       <c r="B197" s="2">
         <v>44169</v>
@@ -20720,7 +20726,7 @@
         <v>25</v>
       </c>
       <c r="F197" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="G197">
         <v>12.5</v>
@@ -20731,7 +20737,7 @@
     </row>
     <row r="198" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A198" t="s">
-        <v>42</v>
+        <v>56</v>
       </c>
       <c r="B198" s="2">
         <v>44172</v>
@@ -20746,7 +20752,7 @@
         <v>25</v>
       </c>
       <c r="F198" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="G198">
         <v>12.5</v>
@@ -20757,7 +20763,7 @@
     </row>
     <row r="199" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A199" t="s">
-        <v>42</v>
+        <v>56</v>
       </c>
       <c r="B199" s="2">
         <v>44174</v>
@@ -20772,7 +20778,7 @@
         <v>25</v>
       </c>
       <c r="F199" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="G199">
         <v>12.5</v>
@@ -20786,7 +20792,7 @@
     </row>
     <row r="200" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A200" t="s">
-        <v>44</v>
+        <v>57</v>
       </c>
       <c r="B200" s="2">
         <v>44138</v>
@@ -20801,7 +20807,7 @@
         <v>25</v>
       </c>
       <c r="F200" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="G200">
         <v>0</v>
@@ -20812,7 +20818,7 @@
     </row>
     <row r="201" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A201" t="s">
-        <v>44</v>
+        <v>57</v>
       </c>
       <c r="B201" s="2">
         <v>44141</v>
@@ -20827,7 +20833,7 @@
         <v>25</v>
       </c>
       <c r="F201" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="G201">
         <v>0</v>
@@ -20838,7 +20844,7 @@
     </row>
     <row r="202" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A202" t="s">
-        <v>44</v>
+        <v>57</v>
       </c>
       <c r="B202" s="2">
         <v>44144</v>
@@ -20853,7 +20859,7 @@
         <v>25</v>
       </c>
       <c r="F202" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="G202">
         <v>0</v>
@@ -20864,7 +20870,7 @@
     </row>
     <row r="203" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A203" t="s">
-        <v>44</v>
+        <v>57</v>
       </c>
       <c r="B203" s="2">
         <v>44146</v>
@@ -20879,7 +20885,7 @@
         <v>25</v>
       </c>
       <c r="F203" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="G203">
         <v>0</v>
@@ -20890,7 +20896,7 @@
     </row>
     <row r="204" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A204" t="s">
-        <v>44</v>
+        <v>57</v>
       </c>
       <c r="B204" s="2">
         <v>44148</v>
@@ -20905,7 +20911,7 @@
         <v>25</v>
       </c>
       <c r="F204" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="G204">
         <v>2</v>
@@ -20916,7 +20922,7 @@
     </row>
     <row r="205" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A205" t="s">
-        <v>44</v>
+        <v>57</v>
       </c>
       <c r="B205" s="2">
         <v>44151</v>
@@ -20931,7 +20937,7 @@
         <v>25</v>
       </c>
       <c r="F205" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="G205">
         <v>7</v>
@@ -20942,7 +20948,7 @@
     </row>
     <row r="206" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A206" t="s">
-        <v>44</v>
+        <v>57</v>
       </c>
       <c r="B206" s="2">
         <v>44153</v>
@@ -20957,7 +20963,7 @@
         <v>25</v>
       </c>
       <c r="F206" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="G206">
         <v>10.5</v>
@@ -20968,7 +20974,7 @@
     </row>
     <row r="207" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A207" t="s">
-        <v>44</v>
+        <v>57</v>
       </c>
       <c r="B207" s="2">
         <v>44155</v>
@@ -20983,7 +20989,7 @@
         <v>25</v>
       </c>
       <c r="F207" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="G207">
         <v>12</v>
@@ -20994,7 +21000,7 @@
     </row>
     <row r="208" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A208" t="s">
-        <v>44</v>
+        <v>57</v>
       </c>
       <c r="B208" s="2">
         <v>44158</v>
@@ -21009,7 +21015,7 @@
         <v>25</v>
       </c>
       <c r="F208" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="G208">
         <v>12.5</v>
@@ -21020,7 +21026,7 @@
     </row>
     <row r="209" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A209" t="s">
-        <v>44</v>
+        <v>57</v>
       </c>
       <c r="B209" s="2">
         <v>44160</v>
@@ -21035,7 +21041,7 @@
         <v>25</v>
       </c>
       <c r="F209" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="G209">
         <v>12.5</v>
@@ -21046,7 +21052,7 @@
     </row>
     <row r="210" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A210" t="s">
-        <v>44</v>
+        <v>57</v>
       </c>
       <c r="B210" s="2">
         <v>44162</v>
@@ -21061,7 +21067,7 @@
         <v>25</v>
       </c>
       <c r="F210" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="G210">
         <v>12.5</v>
@@ -21072,7 +21078,7 @@
     </row>
     <row r="211" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A211" t="s">
-        <v>44</v>
+        <v>57</v>
       </c>
       <c r="B211" s="2">
         <v>44165</v>
@@ -21087,7 +21093,7 @@
         <v>25</v>
       </c>
       <c r="F211" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="G211">
         <v>12.5</v>
@@ -21098,7 +21104,7 @@
     </row>
     <row r="212" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A212" t="s">
-        <v>44</v>
+        <v>57</v>
       </c>
       <c r="B212" s="2">
         <v>44167</v>
@@ -21113,7 +21119,7 @@
         <v>25</v>
       </c>
       <c r="F212" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="G212">
         <v>12.5</v>
@@ -21124,7 +21130,7 @@
     </row>
     <row r="213" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A213" t="s">
-        <v>44</v>
+        <v>57</v>
       </c>
       <c r="B213" s="2">
         <v>44169</v>
@@ -21139,7 +21145,7 @@
         <v>25</v>
       </c>
       <c r="F213" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="G213">
         <v>12.5</v>
@@ -21150,7 +21156,7 @@
     </row>
     <row r="214" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A214" t="s">
-        <v>44</v>
+        <v>57</v>
       </c>
       <c r="B214" s="2">
         <v>44172</v>
@@ -21165,7 +21171,7 @@
         <v>25</v>
       </c>
       <c r="F214" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="G214">
         <v>12.5</v>
@@ -21176,7 +21182,7 @@
     </row>
     <row r="215" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A215" t="s">
-        <v>44</v>
+        <v>57</v>
       </c>
       <c r="B215" s="2">
         <v>44174</v>
@@ -21191,7 +21197,7 @@
         <v>25</v>
       </c>
       <c r="F215" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="G215">
         <v>12.5</v>
@@ -21205,7 +21211,7 @@
     </row>
     <row r="216" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A216" t="s">
-        <v>45</v>
+        <v>58</v>
       </c>
       <c r="B216" s="2">
         <v>44138</v>
@@ -21220,7 +21226,7 @@
         <v>25</v>
       </c>
       <c r="F216" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="G216">
         <v>0</v>
@@ -21231,7 +21237,7 @@
     </row>
     <row r="217" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A217" t="s">
-        <v>45</v>
+        <v>58</v>
       </c>
       <c r="B217" s="2">
         <v>44141</v>
@@ -21246,7 +21252,7 @@
         <v>25</v>
       </c>
       <c r="F217" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="G217">
         <v>0</v>
@@ -21257,7 +21263,7 @@
     </row>
     <row r="218" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A218" t="s">
-        <v>45</v>
+        <v>58</v>
       </c>
       <c r="B218" s="2">
         <v>44144</v>
@@ -21272,7 +21278,7 @@
         <v>25</v>
       </c>
       <c r="F218" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="G218">
         <v>0</v>
@@ -21283,7 +21289,7 @@
     </row>
     <row r="219" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A219" t="s">
-        <v>45</v>
+        <v>58</v>
       </c>
       <c r="B219" s="2">
         <v>44146</v>
@@ -21298,7 +21304,7 @@
         <v>25</v>
       </c>
       <c r="F219" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="G219">
         <v>0</v>
@@ -21309,7 +21315,7 @@
     </row>
     <row r="220" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A220" t="s">
-        <v>45</v>
+        <v>58</v>
       </c>
       <c r="B220" s="2">
         <v>44148</v>
@@ -21324,7 +21330,7 @@
         <v>25</v>
       </c>
       <c r="F220" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="G220">
         <v>2</v>
@@ -21335,7 +21341,7 @@
     </row>
     <row r="221" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A221" t="s">
-        <v>45</v>
+        <v>58</v>
       </c>
       <c r="B221" s="2">
         <v>44151</v>
@@ -21350,7 +21356,7 @@
         <v>25</v>
       </c>
       <c r="F221" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="G221">
         <v>7</v>
@@ -21361,7 +21367,7 @@
     </row>
     <row r="222" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A222" t="s">
-        <v>45</v>
+        <v>58</v>
       </c>
       <c r="B222" s="2">
         <v>44153</v>
@@ -21376,7 +21382,7 @@
         <v>25</v>
       </c>
       <c r="F222" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="G222">
         <v>10.5</v>
@@ -21387,7 +21393,7 @@
     </row>
     <row r="223" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A223" t="s">
-        <v>45</v>
+        <v>58</v>
       </c>
       <c r="B223" s="2">
         <v>44155</v>
@@ -21402,7 +21408,7 @@
         <v>25</v>
       </c>
       <c r="F223" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="G223">
         <v>12</v>
@@ -21413,7 +21419,7 @@
     </row>
     <row r="224" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A224" t="s">
-        <v>45</v>
+        <v>58</v>
       </c>
       <c r="B224" s="2">
         <v>44158</v>
@@ -21428,7 +21434,7 @@
         <v>25</v>
       </c>
       <c r="F224" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="G224">
         <v>12.5</v>
@@ -21439,7 +21445,7 @@
     </row>
     <row r="225" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A225" t="s">
-        <v>45</v>
+        <v>58</v>
       </c>
       <c r="B225" s="2">
         <v>44160</v>
@@ -21454,7 +21460,7 @@
         <v>25</v>
       </c>
       <c r="F225" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="G225">
         <v>12.5</v>
@@ -21465,7 +21471,7 @@
     </row>
     <row r="226" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A226" t="s">
-        <v>45</v>
+        <v>58</v>
       </c>
       <c r="B226" s="2">
         <v>44162</v>
@@ -21480,7 +21486,7 @@
         <v>25</v>
       </c>
       <c r="F226" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="G226">
         <v>12.5</v>
@@ -21491,7 +21497,7 @@
     </row>
     <row r="227" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A227" t="s">
-        <v>45</v>
+        <v>58</v>
       </c>
       <c r="B227" s="2">
         <v>44165</v>
@@ -21506,7 +21512,7 @@
         <v>25</v>
       </c>
       <c r="F227" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="G227">
         <v>12.5</v>
@@ -21517,7 +21523,7 @@
     </row>
     <row r="228" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A228" t="s">
-        <v>45</v>
+        <v>58</v>
       </c>
       <c r="B228" s="2">
         <v>44167</v>
@@ -21532,7 +21538,7 @@
         <v>25</v>
       </c>
       <c r="F228" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="G228">
         <v>12.5</v>
@@ -21543,7 +21549,7 @@
     </row>
     <row r="229" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A229" t="s">
-        <v>45</v>
+        <v>58</v>
       </c>
       <c r="B229" s="2">
         <v>44169</v>
@@ -21558,7 +21564,7 @@
         <v>25</v>
       </c>
       <c r="F229" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="G229">
         <v>12.5</v>
@@ -21569,7 +21575,7 @@
     </row>
     <row r="230" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A230" t="s">
-        <v>45</v>
+        <v>58</v>
       </c>
       <c r="B230" s="2">
         <v>44172</v>
@@ -21584,7 +21590,7 @@
         <v>25</v>
       </c>
       <c r="F230" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="G230">
         <v>12.5</v>
@@ -21595,7 +21601,7 @@
     </row>
     <row r="231" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A231" t="s">
-        <v>45</v>
+        <v>58</v>
       </c>
       <c r="B231" s="2">
         <v>44174</v>
@@ -21610,7 +21616,7 @@
         <v>25</v>
       </c>
       <c r="F231" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="G231">
         <v>12.5</v>
@@ -21624,7 +21630,7 @@
     </row>
     <row r="232" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A232" t="s">
-        <v>46</v>
+        <v>59</v>
       </c>
       <c r="B232" s="2">
         <v>44144</v>
@@ -21639,7 +21645,7 @@
         <v>25</v>
       </c>
       <c r="F232" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="G232">
         <v>0</v>
@@ -21650,7 +21656,7 @@
     </row>
     <row r="233" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A233" t="s">
-        <v>46</v>
+        <v>59</v>
       </c>
       <c r="B233" s="2">
         <v>44146</v>
@@ -21665,7 +21671,7 @@
         <v>25</v>
       </c>
       <c r="F233" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="G233">
         <v>0</v>
@@ -21676,7 +21682,7 @@
     </row>
     <row r="234" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A234" t="s">
-        <v>46</v>
+        <v>59</v>
       </c>
       <c r="B234" s="2">
         <v>44148</v>
@@ -21691,7 +21697,7 @@
         <v>25</v>
       </c>
       <c r="F234" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="G234">
         <v>0</v>
@@ -21702,7 +21708,7 @@
     </row>
     <row r="235" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A235" t="s">
-        <v>46</v>
+        <v>59</v>
       </c>
       <c r="B235" s="2">
         <v>44151</v>
@@ -21717,7 +21723,7 @@
         <v>25</v>
       </c>
       <c r="F235" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="G235">
         <v>4</v>
@@ -21728,7 +21734,7 @@
     </row>
     <row r="236" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A236" t="s">
-        <v>46</v>
+        <v>59</v>
       </c>
       <c r="B236" s="2">
         <v>44153</v>
@@ -21743,7 +21749,7 @@
         <v>25</v>
       </c>
       <c r="F236" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="G236">
         <v>9</v>
@@ -21754,7 +21760,7 @@
     </row>
     <row r="237" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A237" t="s">
-        <v>46</v>
+        <v>59</v>
       </c>
       <c r="B237" s="2">
         <v>44155</v>
@@ -21769,7 +21775,7 @@
         <v>25</v>
       </c>
       <c r="F237" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="G237">
         <v>11</v>
@@ -21780,7 +21786,7 @@
     </row>
     <row r="238" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A238" t="s">
-        <v>46</v>
+        <v>59</v>
       </c>
       <c r="B238" s="2">
         <v>44158</v>
@@ -21795,7 +21801,7 @@
         <v>25</v>
       </c>
       <c r="F238" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="G238">
         <v>12</v>
@@ -21806,7 +21812,7 @@
     </row>
     <row r="239" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A239" t="s">
-        <v>46</v>
+        <v>59</v>
       </c>
       <c r="B239" s="2">
         <v>44160</v>
@@ -21821,7 +21827,7 @@
         <v>25</v>
       </c>
       <c r="F239" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="G239">
         <v>12</v>
@@ -21832,7 +21838,7 @@
     </row>
     <row r="240" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A240" t="s">
-        <v>46</v>
+        <v>59</v>
       </c>
       <c r="B240" s="2">
         <v>44162</v>
@@ -21847,7 +21853,7 @@
         <v>25</v>
       </c>
       <c r="F240" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="G240">
         <v>12</v>
@@ -21858,7 +21864,7 @@
     </row>
     <row r="241" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A241" t="s">
-        <v>46</v>
+        <v>59</v>
       </c>
       <c r="B241" s="2">
         <v>44165</v>
@@ -21873,7 +21879,7 @@
         <v>25</v>
       </c>
       <c r="F241" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="G241">
         <v>12</v>
@@ -21884,7 +21890,7 @@
     </row>
     <row r="242" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A242" t="s">
-        <v>46</v>
+        <v>59</v>
       </c>
       <c r="B242" s="2">
         <v>44167</v>
@@ -21899,7 +21905,7 @@
         <v>25</v>
       </c>
       <c r="F242" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="G242">
         <v>12</v>
@@ -21910,7 +21916,7 @@
     </row>
     <row r="243" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A243" t="s">
-        <v>46</v>
+        <v>59</v>
       </c>
       <c r="B243" s="2">
         <v>44169</v>
@@ -21925,7 +21931,7 @@
         <v>25</v>
       </c>
       <c r="F243" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="G243">
         <v>12</v>
@@ -21936,7 +21942,7 @@
     </row>
     <row r="244" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A244" t="s">
-        <v>46</v>
+        <v>59</v>
       </c>
       <c r="B244" s="2">
         <v>44172</v>
@@ -21951,7 +21957,7 @@
         <v>25</v>
       </c>
       <c r="F244" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="G244">
         <v>12</v>
@@ -21962,7 +21968,7 @@
     </row>
     <row r="245" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A245" t="s">
-        <v>46</v>
+        <v>59</v>
       </c>
       <c r="B245" s="2">
         <v>44174</v>
@@ -21977,7 +21983,7 @@
         <v>25</v>
       </c>
       <c r="F245" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="G245">
         <v>12</v>
@@ -21988,7 +21994,7 @@
     </row>
     <row r="246" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A246" t="s">
-        <v>46</v>
+        <v>59</v>
       </c>
       <c r="B246" s="2">
         <v>44176</v>
@@ -22003,7 +22009,7 @@
         <v>25</v>
       </c>
       <c r="F246" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="G246">
         <v>12</v>
@@ -22014,7 +22020,7 @@
     </row>
     <row r="247" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A247" t="s">
-        <v>46</v>
+        <v>59</v>
       </c>
       <c r="B247" s="2">
         <v>44179</v>
@@ -22029,7 +22035,7 @@
         <v>25</v>
       </c>
       <c r="F247" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="G247">
         <v>12</v>
@@ -22043,7 +22049,7 @@
     </row>
     <row r="248" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A248" t="s">
-        <v>47</v>
+        <v>60</v>
       </c>
       <c r="B248" s="2">
         <v>44144</v>
@@ -22058,7 +22064,7 @@
         <v>25</v>
       </c>
       <c r="F248" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="G248">
         <v>0</v>
@@ -22069,7 +22075,7 @@
     </row>
     <row r="249" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A249" t="s">
-        <v>47</v>
+        <v>60</v>
       </c>
       <c r="B249" s="2">
         <v>44146</v>
@@ -22084,7 +22090,7 @@
         <v>25</v>
       </c>
       <c r="F249" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="G249">
         <v>0</v>
@@ -22095,7 +22101,7 @@
     </row>
     <row r="250" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A250" t="s">
-        <v>47</v>
+        <v>60</v>
       </c>
       <c r="B250" s="2">
         <v>44148</v>
@@ -22110,7 +22116,7 @@
         <v>25</v>
       </c>
       <c r="F250" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="G250">
         <v>0</v>
@@ -22121,7 +22127,7 @@
     </row>
     <row r="251" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A251" t="s">
-        <v>47</v>
+        <v>60</v>
       </c>
       <c r="B251" s="2">
         <v>44151</v>
@@ -22136,7 +22142,7 @@
         <v>25</v>
       </c>
       <c r="F251" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="G251">
         <v>4</v>
@@ -22147,7 +22153,7 @@
     </row>
     <row r="252" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A252" t="s">
-        <v>47</v>
+        <v>60</v>
       </c>
       <c r="B252" s="2">
         <v>44153</v>
@@ -22162,7 +22168,7 @@
         <v>25</v>
       </c>
       <c r="F252" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="G252">
         <v>9</v>
@@ -22173,7 +22179,7 @@
     </row>
     <row r="253" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A253" t="s">
-        <v>47</v>
+        <v>60</v>
       </c>
       <c r="B253" s="2">
         <v>44155</v>
@@ -22188,7 +22194,7 @@
         <v>25</v>
       </c>
       <c r="F253" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="G253">
         <v>11</v>
@@ -22199,7 +22205,7 @@
     </row>
     <row r="254" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A254" t="s">
-        <v>47</v>
+        <v>60</v>
       </c>
       <c r="B254" s="2">
         <v>44158</v>
@@ -22214,7 +22220,7 @@
         <v>25</v>
       </c>
       <c r="F254" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="G254">
         <v>12</v>
@@ -22225,7 +22231,7 @@
     </row>
     <row r="255" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A255" t="s">
-        <v>47</v>
+        <v>60</v>
       </c>
       <c r="B255" s="2">
         <v>44160</v>
@@ -22240,7 +22246,7 @@
         <v>25</v>
       </c>
       <c r="F255" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="G255">
         <v>12</v>
@@ -22251,7 +22257,7 @@
     </row>
     <row r="256" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A256" t="s">
-        <v>47</v>
+        <v>60</v>
       </c>
       <c r="B256" s="2">
         <v>44162</v>
@@ -22266,7 +22272,7 @@
         <v>25</v>
       </c>
       <c r="F256" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="G256">
         <v>12</v>
@@ -22277,7 +22283,7 @@
     </row>
     <row r="257" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A257" t="s">
-        <v>47</v>
+        <v>60</v>
       </c>
       <c r="B257" s="2">
         <v>44165</v>
@@ -22292,7 +22298,7 @@
         <v>25</v>
       </c>
       <c r="F257" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="G257">
         <v>12</v>
@@ -22303,7 +22309,7 @@
     </row>
     <row r="258" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A258" t="s">
-        <v>47</v>
+        <v>60</v>
       </c>
       <c r="B258" s="2">
         <v>44167</v>
@@ -22318,7 +22324,7 @@
         <v>25</v>
       </c>
       <c r="F258" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="G258">
         <v>12</v>
@@ -22329,7 +22335,7 @@
     </row>
     <row r="259" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A259" t="s">
-        <v>47</v>
+        <v>60</v>
       </c>
       <c r="B259" s="2">
         <v>44169</v>
@@ -22344,7 +22350,7 @@
         <v>25</v>
       </c>
       <c r="F259" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="G259">
         <v>12</v>
@@ -22355,7 +22361,7 @@
     </row>
     <row r="260" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A260" t="s">
-        <v>47</v>
+        <v>60</v>
       </c>
       <c r="B260" s="2">
         <v>44172</v>
@@ -22370,7 +22376,7 @@
         <v>25</v>
       </c>
       <c r="F260" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="G260">
         <v>12</v>
@@ -22381,7 +22387,7 @@
     </row>
     <row r="261" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A261" t="s">
-        <v>47</v>
+        <v>60</v>
       </c>
       <c r="B261" s="2">
         <v>44174</v>
@@ -22396,7 +22402,7 @@
         <v>25</v>
       </c>
       <c r="F261" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="G261">
         <v>12</v>
@@ -22407,7 +22413,7 @@
     </row>
     <row r="262" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A262" t="s">
-        <v>47</v>
+        <v>60</v>
       </c>
       <c r="B262" s="2">
         <v>44176</v>
@@ -22422,7 +22428,7 @@
         <v>25</v>
       </c>
       <c r="F262" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="G262">
         <v>12</v>
@@ -22433,7 +22439,7 @@
     </row>
     <row r="263" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A263" t="s">
-        <v>47</v>
+        <v>60</v>
       </c>
       <c r="B263" s="2">
         <v>44179</v>
@@ -22448,7 +22454,7 @@
         <v>25</v>
       </c>
       <c r="F263" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="G263">
         <v>12</v>
@@ -22462,7 +22468,7 @@
     </row>
     <row r="264" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A264" t="s">
-        <v>48</v>
+        <v>61</v>
       </c>
       <c r="B264" s="2">
         <v>44144</v>
@@ -22477,7 +22483,7 @@
         <v>25</v>
       </c>
       <c r="F264" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="G264">
         <v>0</v>
@@ -22488,7 +22494,7 @@
     </row>
     <row r="265" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A265" t="s">
-        <v>48</v>
+        <v>61</v>
       </c>
       <c r="B265" s="2">
         <v>44146</v>
@@ -22503,7 +22509,7 @@
         <v>25</v>
       </c>
       <c r="F265" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="G265">
         <v>0</v>
@@ -22514,7 +22520,7 @@
     </row>
     <row r="266" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A266" t="s">
-        <v>48</v>
+        <v>61</v>
       </c>
       <c r="B266" s="2">
         <v>44148</v>
@@ -22529,7 +22535,7 @@
         <v>25</v>
       </c>
       <c r="F266" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="G266">
         <v>0</v>
@@ -22540,7 +22546,7 @@
     </row>
     <row r="267" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A267" t="s">
-        <v>48</v>
+        <v>61</v>
       </c>
       <c r="B267" s="2">
         <v>44151</v>
@@ -22555,7 +22561,7 @@
         <v>25</v>
       </c>
       <c r="F267" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="G267">
         <v>4</v>
@@ -22566,7 +22572,7 @@
     </row>
     <row r="268" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A268" t="s">
-        <v>48</v>
+        <v>61</v>
       </c>
       <c r="B268" s="2">
         <v>44153</v>
@@ -22581,7 +22587,7 @@
         <v>25</v>
       </c>
       <c r="F268" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="G268">
         <v>9</v>
@@ -22592,7 +22598,7 @@
     </row>
     <row r="269" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A269" t="s">
-        <v>48</v>
+        <v>61</v>
       </c>
       <c r="B269" s="2">
         <v>44155</v>
@@ -22607,7 +22613,7 @@
         <v>25</v>
       </c>
       <c r="F269" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="G269">
         <v>11</v>
@@ -22618,7 +22624,7 @@
     </row>
     <row r="270" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A270" t="s">
-        <v>48</v>
+        <v>61</v>
       </c>
       <c r="B270" s="2">
         <v>44158</v>
@@ -22633,7 +22639,7 @@
         <v>25</v>
       </c>
       <c r="F270" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="G270">
         <v>12</v>
@@ -22644,7 +22650,7 @@
     </row>
     <row r="271" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A271" t="s">
-        <v>48</v>
+        <v>61</v>
       </c>
       <c r="B271" s="2">
         <v>44160</v>
@@ -22659,7 +22665,7 @@
         <v>25</v>
       </c>
       <c r="F271" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="G271">
         <v>12</v>
@@ -22670,7 +22676,7 @@
     </row>
     <row r="272" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A272" t="s">
-        <v>48</v>
+        <v>61</v>
       </c>
       <c r="B272" s="2">
         <v>44162</v>
@@ -22685,7 +22691,7 @@
         <v>25</v>
       </c>
       <c r="F272" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="G272">
         <v>12</v>
@@ -22696,7 +22702,7 @@
     </row>
     <row r="273" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A273" t="s">
-        <v>48</v>
+        <v>61</v>
       </c>
       <c r="B273" s="2">
         <v>44165</v>
@@ -22711,7 +22717,7 @@
         <v>25</v>
       </c>
       <c r="F273" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="G273">
         <v>12</v>
@@ -22722,7 +22728,7 @@
     </row>
     <row r="274" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A274" t="s">
-        <v>48</v>
+        <v>61</v>
       </c>
       <c r="B274" s="2">
         <v>44167</v>
@@ -22737,7 +22743,7 @@
         <v>25</v>
       </c>
       <c r="F274" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="G274">
         <v>12</v>
@@ -22748,7 +22754,7 @@
     </row>
     <row r="275" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A275" t="s">
-        <v>48</v>
+        <v>61</v>
       </c>
       <c r="B275" s="2">
         <v>44169</v>
@@ -22763,7 +22769,7 @@
         <v>25</v>
       </c>
       <c r="F275" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="G275">
         <v>12</v>
@@ -22774,7 +22780,7 @@
     </row>
     <row r="276" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A276" t="s">
-        <v>48</v>
+        <v>61</v>
       </c>
       <c r="B276" s="2">
         <v>44172</v>
@@ -22789,7 +22795,7 @@
         <v>25</v>
       </c>
       <c r="F276" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="G276">
         <v>12</v>
@@ -22800,7 +22806,7 @@
     </row>
     <row r="277" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A277" t="s">
-        <v>48</v>
+        <v>61</v>
       </c>
       <c r="B277" s="2">
         <v>44174</v>
@@ -22815,7 +22821,7 @@
         <v>25</v>
       </c>
       <c r="F277" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="G277">
         <v>12</v>
@@ -22826,7 +22832,7 @@
     </row>
     <row r="278" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A278" t="s">
-        <v>48</v>
+        <v>61</v>
       </c>
       <c r="B278" s="2">
         <v>44176</v>
@@ -22841,7 +22847,7 @@
         <v>25</v>
       </c>
       <c r="F278" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="G278">
         <v>12</v>
@@ -22852,7 +22858,7 @@
     </row>
     <row r="279" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A279" t="s">
-        <v>48</v>
+        <v>61</v>
       </c>
       <c r="B279" s="2">
         <v>44179</v>
@@ -22867,7 +22873,7 @@
         <v>25</v>
       </c>
       <c r="F279" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="G279">
         <v>12</v>
@@ -22881,7 +22887,7 @@
     </row>
     <row r="280" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A280" t="s">
-        <v>49</v>
+        <v>39</v>
       </c>
       <c r="B280" s="2">
         <v>44138</v>
@@ -22907,7 +22913,7 @@
     </row>
     <row r="281" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A281" t="s">
-        <v>49</v>
+        <v>39</v>
       </c>
       <c r="B281" s="2">
         <v>44141</v>
@@ -22933,7 +22939,7 @@
     </row>
     <row r="282" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A282" t="s">
-        <v>49</v>
+        <v>39</v>
       </c>
       <c r="B282" s="2">
         <v>44144</v>
@@ -22959,7 +22965,7 @@
     </row>
     <row r="283" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A283" t="s">
-        <v>49</v>
+        <v>39</v>
       </c>
       <c r="B283" s="2">
         <v>44147</v>
@@ -22985,7 +22991,7 @@
     </row>
     <row r="284" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A284" t="s">
-        <v>49</v>
+        <v>39</v>
       </c>
       <c r="B284" s="2">
         <v>44151</v>
@@ -23011,7 +23017,7 @@
     </row>
     <row r="285" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A285" t="s">
-        <v>49</v>
+        <v>39</v>
       </c>
       <c r="B285" s="2">
         <v>44154</v>
@@ -23037,7 +23043,7 @@
     </row>
     <row r="286" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A286" t="s">
-        <v>49</v>
+        <v>39</v>
       </c>
       <c r="B286" s="2">
         <v>44158</v>
@@ -23063,7 +23069,7 @@
     </row>
     <row r="287" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A287" t="s">
-        <v>49</v>
+        <v>39</v>
       </c>
       <c r="B287" s="2">
         <v>44162</v>
@@ -23089,7 +23095,7 @@
     </row>
     <row r="288" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A288" t="s">
-        <v>49</v>
+        <v>39</v>
       </c>
       <c r="B288" s="2">
         <v>44166</v>
@@ -23115,7 +23121,7 @@
     </row>
     <row r="289" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A289" t="s">
-        <v>49</v>
+        <v>39</v>
       </c>
       <c r="B289" s="2">
         <v>44169</v>
@@ -23141,7 +23147,7 @@
     </row>
     <row r="290" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A290" t="s">
-        <v>49</v>
+        <v>39</v>
       </c>
       <c r="B290" s="2">
         <v>44172</v>
@@ -23167,7 +23173,7 @@
     </row>
     <row r="291" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A291" t="s">
-        <v>49</v>
+        <v>39</v>
       </c>
       <c r="B291" s="2">
         <v>44175</v>
@@ -23193,7 +23199,7 @@
     </row>
     <row r="292" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A292" t="s">
-        <v>49</v>
+        <v>39</v>
       </c>
       <c r="B292" s="2">
         <v>44176</v>
@@ -23222,7 +23228,7 @@
     </row>
     <row r="293" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A293" t="s">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="B293" s="2">
         <v>44138</v>
@@ -23248,7 +23254,7 @@
     </row>
     <row r="294" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A294" t="s">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="B294" s="2">
         <v>44141</v>
@@ -23274,7 +23280,7 @@
     </row>
     <row r="295" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A295" t="s">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="B295" s="2">
         <v>44144</v>
@@ -23300,7 +23306,7 @@
     </row>
     <row r="296" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A296" t="s">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="B296" s="2">
         <v>44147</v>
@@ -23326,7 +23332,7 @@
     </row>
     <row r="297" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A297" t="s">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="B297" s="2">
         <v>44151</v>
@@ -23352,7 +23358,7 @@
     </row>
     <row r="298" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A298" t="s">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="B298" s="2">
         <v>44154</v>
@@ -23378,7 +23384,7 @@
     </row>
     <row r="299" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A299" t="s">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="B299" s="2">
         <v>44158</v>
@@ -23404,7 +23410,7 @@
     </row>
     <row r="300" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A300" t="s">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="B300" s="2">
         <v>44162</v>
@@ -23430,7 +23436,7 @@
     </row>
     <row r="301" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A301" t="s">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="B301" s="2">
         <v>44166</v>
@@ -23456,7 +23462,7 @@
     </row>
     <row r="302" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A302" t="s">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="B302" s="2">
         <v>44169</v>
@@ -23482,7 +23488,7 @@
     </row>
     <row r="303" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A303" t="s">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="B303" s="2">
         <v>44172</v>
@@ -23508,7 +23514,7 @@
     </row>
     <row r="304" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A304" t="s">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="B304" s="2">
         <v>44175</v>
@@ -23534,7 +23540,7 @@
     </row>
     <row r="305" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A305" t="s">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="B305" s="2">
         <v>44176</v>
@@ -23563,7 +23569,7 @@
     </row>
     <row r="306" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A306" t="s">
-        <v>51</v>
+        <v>41</v>
       </c>
       <c r="B306" s="2">
         <v>44138</v>
@@ -23589,7 +23595,7 @@
     </row>
     <row r="307" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A307" t="s">
-        <v>51</v>
+        <v>41</v>
       </c>
       <c r="B307" s="2">
         <v>44141</v>
@@ -23615,7 +23621,7 @@
     </row>
     <row r="308" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A308" t="s">
-        <v>51</v>
+        <v>41</v>
       </c>
       <c r="B308" s="2">
         <v>44144</v>
@@ -23641,7 +23647,7 @@
     </row>
     <row r="309" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A309" t="s">
-        <v>51</v>
+        <v>41</v>
       </c>
       <c r="B309" s="2">
         <v>44147</v>
@@ -23667,7 +23673,7 @@
     </row>
     <row r="310" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A310" t="s">
-        <v>51</v>
+        <v>41</v>
       </c>
       <c r="B310" s="2">
         <v>44151</v>
@@ -23693,7 +23699,7 @@
     </row>
     <row r="311" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A311" t="s">
-        <v>51</v>
+        <v>41</v>
       </c>
       <c r="B311" s="2">
         <v>44154</v>
@@ -23719,7 +23725,7 @@
     </row>
     <row r="312" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A312" t="s">
-        <v>51</v>
+        <v>41</v>
       </c>
       <c r="B312" s="2">
         <v>44158</v>
@@ -23745,7 +23751,7 @@
     </row>
     <row r="313" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A313" t="s">
-        <v>51</v>
+        <v>41</v>
       </c>
       <c r="B313" s="2">
         <v>44162</v>
@@ -23771,7 +23777,7 @@
     </row>
     <row r="314" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A314" t="s">
-        <v>51</v>
+        <v>41</v>
       </c>
       <c r="B314" s="2">
         <v>44166</v>
@@ -23797,7 +23803,7 @@
     </row>
     <row r="315" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A315" t="s">
-        <v>51</v>
+        <v>41</v>
       </c>
       <c r="B315" s="2">
         <v>44169</v>
@@ -23823,7 +23829,7 @@
     </row>
     <row r="316" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A316" t="s">
-        <v>51</v>
+        <v>41</v>
       </c>
       <c r="B316" s="2">
         <v>44172</v>
@@ -23849,7 +23855,7 @@
     </row>
     <row r="317" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A317" t="s">
-        <v>51</v>
+        <v>41</v>
       </c>
       <c r="B317" s="2">
         <v>44175</v>
@@ -23875,7 +23881,7 @@
     </row>
     <row r="318" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A318" t="s">
-        <v>51</v>
+        <v>41</v>
       </c>
       <c r="B318" s="2">
         <v>44176</v>
@@ -23904,7 +23910,7 @@
     </row>
     <row r="319" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A319" t="s">
-        <v>52</v>
+        <v>42</v>
       </c>
       <c r="B319" s="2">
         <v>44508</v>
@@ -23930,7 +23936,7 @@
     </row>
     <row r="320" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A320" t="s">
-        <v>52</v>
+        <v>42</v>
       </c>
       <c r="B320" s="2">
         <v>44509</v>
@@ -23956,7 +23962,7 @@
     </row>
     <row r="321" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A321" t="s">
-        <v>52</v>
+        <v>42</v>
       </c>
       <c r="B321" s="2">
         <v>44512</v>
@@ -23982,7 +23988,7 @@
     </row>
     <row r="322" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A322" t="s">
-        <v>52</v>
+        <v>42</v>
       </c>
       <c r="B322" s="2">
         <v>44516</v>
@@ -24008,7 +24014,7 @@
     </row>
     <row r="323" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A323" t="s">
-        <v>52</v>
+        <v>42</v>
       </c>
       <c r="B323" s="2">
         <v>44519</v>
@@ -24034,7 +24040,7 @@
     </row>
     <row r="324" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A324" t="s">
-        <v>52</v>
+        <v>42</v>
       </c>
       <c r="B324" s="2">
         <v>44523</v>
@@ -24060,7 +24066,7 @@
     </row>
     <row r="325" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A325" t="s">
-        <v>52</v>
+        <v>42</v>
       </c>
       <c r="B325" s="2">
         <v>44526</v>
@@ -24086,7 +24092,7 @@
     </row>
     <row r="326" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A326" t="s">
-        <v>52</v>
+        <v>42</v>
       </c>
       <c r="B326" s="2">
         <v>44530</v>
@@ -24112,7 +24118,7 @@
     </row>
     <row r="327" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A327" t="s">
-        <v>52</v>
+        <v>42</v>
       </c>
       <c r="B327" s="2">
         <v>44533</v>
@@ -24141,7 +24147,7 @@
     </row>
     <row r="328" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A328" t="s">
-        <v>53</v>
+        <v>43</v>
       </c>
       <c r="B328" s="2">
         <v>44508</v>
@@ -24167,7 +24173,7 @@
     </row>
     <row r="329" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A329" t="s">
-        <v>53</v>
+        <v>43</v>
       </c>
       <c r="B329" s="2">
         <v>44509</v>
@@ -24193,7 +24199,7 @@
     </row>
     <row r="330" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A330" t="s">
-        <v>53</v>
+        <v>43</v>
       </c>
       <c r="B330" s="2">
         <v>44512</v>
@@ -24219,7 +24225,7 @@
     </row>
     <row r="331" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A331" t="s">
-        <v>53</v>
+        <v>43</v>
       </c>
       <c r="B331" s="2">
         <v>44516</v>
@@ -24245,7 +24251,7 @@
     </row>
     <row r="332" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A332" t="s">
-        <v>53</v>
+        <v>43</v>
       </c>
       <c r="B332" s="2">
         <v>44519</v>
@@ -24271,7 +24277,7 @@
     </row>
     <row r="333" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A333" t="s">
-        <v>53</v>
+        <v>43</v>
       </c>
       <c r="B333" s="2">
         <v>44523</v>
@@ -24297,7 +24303,7 @@
     </row>
     <row r="334" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A334" t="s">
-        <v>53</v>
+        <v>43</v>
       </c>
       <c r="B334" s="2">
         <v>44526</v>
@@ -24323,7 +24329,7 @@
     </row>
     <row r="335" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A335" t="s">
-        <v>53</v>
+        <v>43</v>
       </c>
       <c r="B335" s="2">
         <v>44530</v>
@@ -24349,7 +24355,7 @@
     </row>
     <row r="336" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A336" t="s">
-        <v>53</v>
+        <v>43</v>
       </c>
       <c r="B336" s="2">
         <v>44533</v>
@@ -24378,7 +24384,7 @@
     </row>
     <row r="337" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A337" t="s">
-        <v>54</v>
+        <v>44</v>
       </c>
       <c r="B337" s="2">
         <v>44508</v>
@@ -24404,7 +24410,7 @@
     </row>
     <row r="338" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A338" t="s">
-        <v>54</v>
+        <v>44</v>
       </c>
       <c r="B338" s="2">
         <v>44509</v>
@@ -24430,7 +24436,7 @@
     </row>
     <row r="339" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A339" t="s">
-        <v>54</v>
+        <v>44</v>
       </c>
       <c r="B339" s="2">
         <v>44512</v>
@@ -24456,7 +24462,7 @@
     </row>
     <row r="340" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A340" t="s">
-        <v>54</v>
+        <v>44</v>
       </c>
       <c r="B340" s="2">
         <v>44516</v>
@@ -24482,7 +24488,7 @@
     </row>
     <row r="341" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A341" t="s">
-        <v>54</v>
+        <v>44</v>
       </c>
       <c r="B341" s="2">
         <v>44519</v>
@@ -24508,7 +24514,7 @@
     </row>
     <row r="342" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A342" t="s">
-        <v>54</v>
+        <v>44</v>
       </c>
       <c r="B342" s="2">
         <v>44523</v>
@@ -24534,7 +24540,7 @@
     </row>
     <row r="343" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A343" t="s">
-        <v>54</v>
+        <v>44</v>
       </c>
       <c r="B343" s="2">
         <v>44526</v>
@@ -24560,7 +24566,7 @@
     </row>
     <row r="344" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A344" t="s">
-        <v>54</v>
+        <v>44</v>
       </c>
       <c r="B344" s="2">
         <v>44530</v>
@@ -24586,7 +24592,7 @@
     </row>
     <row r="345" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A345" t="s">
-        <v>54</v>
+        <v>44</v>
       </c>
       <c r="B345" s="2">
         <v>44533</v>
@@ -24615,7 +24621,7 @@
     </row>
     <row r="346" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A346" t="s">
-        <v>55</v>
+        <v>45</v>
       </c>
       <c r="B346" s="2">
         <v>44508</v>
@@ -24641,7 +24647,7 @@
     </row>
     <row r="347" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A347" t="s">
-        <v>55</v>
+        <v>45</v>
       </c>
       <c r="B347" s="2">
         <v>44509</v>
@@ -24667,7 +24673,7 @@
     </row>
     <row r="348" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A348" t="s">
-        <v>55</v>
+        <v>45</v>
       </c>
       <c r="B348" s="2">
         <v>44512</v>
@@ -24693,7 +24699,7 @@
     </row>
     <row r="349" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A349" t="s">
-        <v>55</v>
+        <v>45</v>
       </c>
       <c r="B349" s="2">
         <v>44516</v>
@@ -24719,7 +24725,7 @@
     </row>
     <row r="350" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A350" t="s">
-        <v>55</v>
+        <v>45</v>
       </c>
       <c r="B350" s="2">
         <v>44519</v>
@@ -24745,7 +24751,7 @@
     </row>
     <row r="351" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A351" t="s">
-        <v>55</v>
+        <v>45</v>
       </c>
       <c r="B351" s="2">
         <v>44523</v>
@@ -24771,7 +24777,7 @@
     </row>
     <row r="352" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A352" t="s">
-        <v>55</v>
+        <v>45</v>
       </c>
       <c r="B352" s="2">
         <v>44526</v>
@@ -24797,7 +24803,7 @@
     </row>
     <row r="353" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A353" t="s">
-        <v>55</v>
+        <v>45</v>
       </c>
       <c r="B353" s="2">
         <v>44530</v>
@@ -24823,7 +24829,7 @@
     </row>
     <row r="354" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A354" t="s">
-        <v>55</v>
+        <v>45</v>
       </c>
       <c r="B354" s="2">
         <v>44533</v>
@@ -24852,7 +24858,7 @@
     </row>
     <row r="355" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A355" t="s">
-        <v>56</v>
+        <v>46</v>
       </c>
       <c r="B355" s="2">
         <v>44508</v>
@@ -24878,7 +24884,7 @@
     </row>
     <row r="356" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A356" t="s">
-        <v>56</v>
+        <v>46</v>
       </c>
       <c r="B356" s="2">
         <v>44509</v>
@@ -24904,7 +24910,7 @@
     </row>
     <row r="357" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A357" t="s">
-        <v>56</v>
+        <v>46</v>
       </c>
       <c r="B357" s="2">
         <v>44512</v>
@@ -24930,7 +24936,7 @@
     </row>
     <row r="358" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A358" t="s">
-        <v>56</v>
+        <v>46</v>
       </c>
       <c r="B358" s="2">
         <v>44516</v>
@@ -24956,7 +24962,7 @@
     </row>
     <row r="359" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A359" t="s">
-        <v>56</v>
+        <v>46</v>
       </c>
       <c r="B359" s="2">
         <v>44519</v>
@@ -24982,7 +24988,7 @@
     </row>
     <row r="360" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A360" t="s">
-        <v>56</v>
+        <v>46</v>
       </c>
       <c r="B360" s="2">
         <v>44523</v>
@@ -25008,7 +25014,7 @@
     </row>
     <row r="361" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A361" t="s">
-        <v>56</v>
+        <v>46</v>
       </c>
       <c r="B361" s="2">
         <v>44526</v>
@@ -25034,7 +25040,7 @@
     </row>
     <row r="362" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A362" t="s">
-        <v>56</v>
+        <v>46</v>
       </c>
       <c r="B362" s="2">
         <v>44530</v>
@@ -25060,7 +25066,7 @@
     </row>
     <row r="363" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A363" t="s">
-        <v>56</v>
+        <v>46</v>
       </c>
       <c r="B363" s="2">
         <v>44533</v>
@@ -25089,7 +25095,7 @@
     </row>
     <row r="364" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A364" t="s">
-        <v>57</v>
+        <v>47</v>
       </c>
       <c r="B364" s="2">
         <v>44147</v>
@@ -25115,7 +25121,7 @@
     </row>
     <row r="365" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A365" t="s">
-        <v>57</v>
+        <v>47</v>
       </c>
       <c r="B365" s="2">
         <v>44151</v>
@@ -25141,7 +25147,7 @@
     </row>
     <row r="366" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A366" t="s">
-        <v>57</v>
+        <v>47</v>
       </c>
       <c r="B366" s="2">
         <v>44154</v>
@@ -25167,7 +25173,7 @@
     </row>
     <row r="367" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A367" t="s">
-        <v>57</v>
+        <v>47</v>
       </c>
       <c r="B367" s="2">
         <v>44159</v>
@@ -25193,7 +25199,7 @@
     </row>
     <row r="368" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A368" t="s">
-        <v>57</v>
+        <v>47</v>
       </c>
       <c r="B368" s="2">
         <v>44162</v>
@@ -25219,7 +25225,7 @@
     </row>
     <row r="369" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A369" t="s">
-        <v>57</v>
+        <v>47</v>
       </c>
       <c r="B369" s="2">
         <v>44166</v>
@@ -25245,7 +25251,7 @@
     </row>
     <row r="370" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A370" t="s">
-        <v>57</v>
+        <v>47</v>
       </c>
       <c r="B370" s="2">
         <v>44169</v>
@@ -25274,7 +25280,7 @@
     </row>
     <row r="371" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A371" t="s">
-        <v>58</v>
+        <v>48</v>
       </c>
       <c r="B371" s="2">
         <v>44147</v>
@@ -25300,7 +25306,7 @@
     </row>
     <row r="372" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A372" t="s">
-        <v>58</v>
+        <v>48</v>
       </c>
       <c r="B372" s="2">
         <v>44151</v>
@@ -25326,7 +25332,7 @@
     </row>
     <row r="373" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A373" t="s">
-        <v>58</v>
+        <v>48</v>
       </c>
       <c r="B373" s="2">
         <v>44154</v>
@@ -25352,7 +25358,7 @@
     </row>
     <row r="374" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A374" t="s">
-        <v>58</v>
+        <v>48</v>
       </c>
       <c r="B374" s="2">
         <v>44159</v>
@@ -25378,7 +25384,7 @@
     </row>
     <row r="375" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A375" t="s">
-        <v>58</v>
+        <v>48</v>
       </c>
       <c r="B375" s="2">
         <v>44162</v>
@@ -25404,7 +25410,7 @@
     </row>
     <row r="376" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A376" t="s">
-        <v>58</v>
+        <v>48</v>
       </c>
       <c r="B376" s="2">
         <v>44166</v>
@@ -25430,7 +25436,7 @@
     </row>
     <row r="377" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A377" t="s">
-        <v>58</v>
+        <v>48</v>
       </c>
       <c r="B377" s="2">
         <v>44169</v>
@@ -25459,7 +25465,7 @@
     </row>
     <row r="378" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A378" t="s">
-        <v>59</v>
+        <v>49</v>
       </c>
       <c r="B378" s="2">
         <v>44147</v>
@@ -25485,7 +25491,7 @@
     </row>
     <row r="379" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A379" t="s">
-        <v>59</v>
+        <v>49</v>
       </c>
       <c r="B379" s="2">
         <v>44151</v>
@@ -25511,7 +25517,7 @@
     </row>
     <row r="380" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A380" t="s">
-        <v>59</v>
+        <v>49</v>
       </c>
       <c r="B380" s="2">
         <v>44154</v>
@@ -25537,7 +25543,7 @@
     </row>
     <row r="381" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A381" t="s">
-        <v>59</v>
+        <v>49</v>
       </c>
       <c r="B381" s="2">
         <v>44159</v>
@@ -25563,7 +25569,7 @@
     </row>
     <row r="382" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A382" t="s">
-        <v>59</v>
+        <v>49</v>
       </c>
       <c r="B382" s="2">
         <v>44162</v>
@@ -25589,7 +25595,7 @@
     </row>
     <row r="383" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A383" t="s">
-        <v>59</v>
+        <v>49</v>
       </c>
       <c r="B383" s="2">
         <v>44166</v>
@@ -25615,7 +25621,7 @@
     </row>
     <row r="384" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A384" t="s">
-        <v>59</v>
+        <v>49</v>
       </c>
       <c r="B384" s="2">
         <v>44169</v>
